--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0022C4EB-C89D-7040-AE3C-627C2E82FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B4C1B5-3446-7A45-8E0C-7EF7ACA52511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="161">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -517,6 +517,12 @@
   </si>
   <si>
     <t>Reid H.</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-10</t>
+  </si>
+  <si>
+    <t>Thursday 9/10/26</t>
   </si>
 </sst>
 </file>
@@ -1067,44 +1073,6 @@
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1118,8 +1086,46 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1167,6 +1173,35 @@
           <bgColor rgb="FFE5E7EB"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF17231D"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFE3EAE6"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1373,35 +1408,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF17231D"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFE3EAE6"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1433,24 +1439,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="28">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I17" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I18" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1467,15 +1473,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D117" totalsRowShown="0" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D124" totalsRowShown="0" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1485,7 +1491,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EventPhotosTable" displayName="EventPhotosTable" ref="A4:E8" totalsRowShown="0">
   <autoFilter ref="A4:E8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Image Path"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Caption"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Show on Home"/>
@@ -1496,16 +1502,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A4:G7" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Date" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Title" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Body" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Date" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Title" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Body" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1514,7 +1520,7 @@
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="BlindSchedulesTable" displayName="BlindSchedulesTable" ref="A4:E38" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Level"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Duration"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Small Blind"/>
@@ -1729,106 +1735,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="76" t="s">
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="73" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="76" t="s">
+      <c r="A2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="73" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="77" t="s">
+      <c r="E3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="77" t="s">
+      <c r="G3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="74" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="78" t="s">
+      <c r="D5" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="78" t="s">
+      <c r="E5" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="75" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1836,22 +1842,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="77" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1863,22 +1869,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="79" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1890,49 +1896,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="77" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F9" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="79" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1944,22 +1950,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="77" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1971,237 +1977,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="74" t="s">
+      <c r="F11" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="79" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="75" t="s">
+      <c r="G14" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="75" t="s">
+      <c r="H14" s="80" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="E15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="72" t="s">
+      <c r="H15" s="76" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="71" t="s">
+      <c r="E16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="71" t="s">
+      <c r="G16" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="78" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="72" t="s">
+      <c r="A17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="76" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="71" t="s">
+      <c r="G18" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="78" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="72" t="s">
+      <c r="H19" s="76" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="71" t="s">
+      <c r="E20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="71" t="s">
+      <c r="F20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="71" t="s">
+      <c r="G20" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="71" t="s">
+      <c r="H20" s="78" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2226,89 +2232,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="81" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="82" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="83" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2488,43 +2494,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9" ht="27" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
     </row>
     <row r="3" spans="1:9" ht="27" customHeight="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3769,7 +3775,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3786,89 +3792,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="81" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="82" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="83" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4240,6 +4246,32 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="28">
+        <v>46275</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H18">
         <v>20</v>
       </c>
     </row>
@@ -4256,7 +4288,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F17" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G5:G199 F5:F18" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4273,7 +4305,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -4284,28 +4316,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -5901,6 +5933,104 @@
       </c>
       <c r="D117" s="14">
         <v>26.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="25" customHeight="1">
+      <c r="A118" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C118" s="14">
+        <v>20</v>
+      </c>
+      <c r="D118" s="14">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="25" customHeight="1">
+      <c r="A119" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C119" s="14">
+        <v>20</v>
+      </c>
+      <c r="D119" s="14">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="25" customHeight="1">
+      <c r="A120" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C120" s="14">
+        <v>40</v>
+      </c>
+      <c r="D120" s="14">
+        <v>51.75</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="25" customHeight="1">
+      <c r="A121" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C121" s="14">
+        <v>70</v>
+      </c>
+      <c r="D121" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="25" customHeight="1">
+      <c r="A122" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C122" s="14">
+        <v>60</v>
+      </c>
+      <c r="D122" s="14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="25" customHeight="1">
+      <c r="A123" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C123" s="14">
+        <v>40</v>
+      </c>
+      <c r="D123" s="14">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="25" customHeight="1">
+      <c r="A124" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C124" s="14">
+        <v>20</v>
+      </c>
+      <c r="D124" s="14">
+        <v>38.75</v>
       </c>
     </row>
   </sheetData>
@@ -5939,53 +6069,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="81" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="82" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="83" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6106,71 +6236,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="81" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="82" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="83" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6284,31 +6414,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="85" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="86" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="66" t="s">

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B4C1B5-3446-7A45-8E0C-7EF7ACA52511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F403177-74A8-1847-ABB3-E3F19D921AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="168">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -523,6 +523,27 @@
   </si>
   <si>
     <t>Thursday 9/10/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-12</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-16</t>
+  </si>
+  <si>
+    <t>Saturday 9/12/26</t>
+  </si>
+  <si>
+    <t>Wednesday 9/16/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-19</t>
+  </si>
+  <si>
+    <t>Saturday 9/19/26</t>
+  </si>
+  <si>
+    <t>Wyatt</t>
   </si>
 </sst>
 </file>
@@ -1076,16 +1097,25 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1095,19 +1125,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1117,8 +1134,12 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1293,16 +1314,6 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1383,6 +1394,16 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1439,24 +1460,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="23">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I18" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I21" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1473,15 +1494,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D124" totalsRowShown="0" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D143" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1735,106 +1756,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="73" t="s">
+      <c r="A1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="76" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="73" t="s">
+      <c r="A2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="76" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="74" t="s">
+      <c r="G3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="74" t="s">
+      <c r="H3" s="77" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="75" t="s">
+      <c r="H5" s="78" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1842,22 +1863,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="76" t="s">
+      <c r="E6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="77" t="s">
+      <c r="G6" s="73" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1869,22 +1890,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="74" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1896,49 +1917,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="76" t="s">
+      <c r="C8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="76" t="s">
+      <c r="E8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="77" t="s">
+      <c r="G8" s="73" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="78" t="s">
+      <c r="D9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="79" t="s">
+      <c r="F9" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="79" t="s">
+      <c r="G9" s="74" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1950,22 +1971,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="73" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -1977,237 +1998,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="74" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>173</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="80" t="s">
+      <c r="D14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="80" t="s">
+      <c r="E14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="80" t="s">
+      <c r="F14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="80" t="s">
+      <c r="G14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="80" t="s">
+      <c r="H14" s="75" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="76" t="s">
+      <c r="A15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="76" t="s">
+      <c r="E15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="76" t="s">
+      <c r="G15" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="76" t="s">
+      <c r="H15" s="72" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="78" t="s">
+      <c r="D16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="78" t="s">
+      <c r="F16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="78" t="s">
+      <c r="G16" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="71" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="76" t="s">
+      <c r="A17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="72" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="78" t="s">
+      <c r="D18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="78" t="s">
+      <c r="F18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="78" t="s">
+      <c r="G18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="78" t="s">
+      <c r="H18" s="71" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="76" t="s">
+      <c r="F19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="76" t="s">
+      <c r="G19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="76" t="s">
+      <c r="H19" s="72" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="78" t="s">
+      <c r="D20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="78" t="s">
+      <c r="F20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="78" t="s">
+      <c r="G20" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="78" t="s">
+      <c r="H20" s="71" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2232,89 +2253,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="81" t="s">
+      <c r="F1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="81" t="s">
+      <c r="H1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="81" t="s">
+      <c r="I1" s="79" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="F2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="82" t="s">
+      <c r="G2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="H2" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="80" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="F3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="83" t="s">
+      <c r="H3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="83" t="s">
+      <c r="I3" s="81" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2503,34 +2524,34 @@
       <c r="E1" s="68"/>
       <c r="F1" s="68"/>
       <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:9" ht="27" customHeight="1">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
     </row>
     <row r="3" spans="1:9" ht="27" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3775,7 +3796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3792,89 +3813,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="81" t="s">
+      <c r="F1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="81" t="s">
+      <c r="H1" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="81" t="s">
+      <c r="I1" s="79" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="F2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="82" t="s">
+      <c r="G2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="H2" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="80" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="F3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="83" t="s">
+      <c r="H3" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="83" t="s">
+      <c r="I3" s="81" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4115,7 +4136,7 @@
       <c r="G12" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4141,7 +4162,7 @@
       <c r="G13" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4167,7 +4188,7 @@
       <c r="G14" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4193,7 +4214,7 @@
       <c r="G15" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4219,7 +4240,7 @@
       <c r="G16" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4245,7 +4266,7 @@
       <c r="G17" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4271,7 +4292,85 @@
       <c r="G18" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="28">
+        <v>46277</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H19" s="63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="28">
+        <v>46281</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H20" s="63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="28">
+        <v>46284</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H21" s="63">
         <v>20</v>
       </c>
     </row>
@@ -4288,7 +4387,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="G5:G199 F5:F18" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F21 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4305,7 +4404,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -4324,20 +4423,20 @@
       <c r="D1" s="68"/>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -6031,6 +6130,272 @@
       </c>
       <c r="D124" s="14">
         <v>38.75</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="25" customHeight="1">
+      <c r="A125" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C125" s="14">
+        <v>40</v>
+      </c>
+      <c r="D125" s="14">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="25" customHeight="1">
+      <c r="A126" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C126" s="14">
+        <v>40</v>
+      </c>
+      <c r="D126" s="14">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="25" customHeight="1">
+      <c r="A127" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C127" s="14">
+        <v>40</v>
+      </c>
+      <c r="D127" s="14">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="25" customHeight="1">
+      <c r="A128" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C128" s="14">
+        <v>20</v>
+      </c>
+      <c r="D128" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="25" customHeight="1">
+      <c r="A129" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C129" s="14">
+        <v>20</v>
+      </c>
+      <c r="D129" s="14">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="25" customHeight="1">
+      <c r="A130" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C130" s="14">
+        <v>20</v>
+      </c>
+      <c r="D130" s="14">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="25" customHeight="1">
+      <c r="A131" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C131" s="14">
+        <v>20</v>
+      </c>
+      <c r="D131" s="14">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="25" customHeight="1">
+      <c r="A132" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C132" s="14">
+        <v>20</v>
+      </c>
+      <c r="D132" s="14">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="25" customHeight="1">
+      <c r="A133" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C133" s="14">
+        <v>20</v>
+      </c>
+      <c r="D133" s="14">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="25" customHeight="1">
+      <c r="A134" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C134" s="14">
+        <v>20</v>
+      </c>
+      <c r="D134" s="14">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="25" customHeight="1">
+      <c r="A135" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C135" s="14">
+        <v>20</v>
+      </c>
+      <c r="D135" s="14">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="25" customHeight="1">
+      <c r="A136" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C136" s="14">
+        <v>20</v>
+      </c>
+      <c r="D136" s="14">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="25" customHeight="1">
+      <c r="A137" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C137" s="14">
+        <v>20</v>
+      </c>
+      <c r="D137" s="14">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="25" customHeight="1">
+      <c r="A138" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C138" s="14">
+        <v>20</v>
+      </c>
+      <c r="D138" s="14">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="25" customHeight="1">
+      <c r="A139" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C139" s="14">
+        <v>40</v>
+      </c>
+      <c r="D139" s="14">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="25" customHeight="1">
+      <c r="A140" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C140" s="14">
+        <v>80</v>
+      </c>
+      <c r="D140" s="14">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="25" customHeight="1">
+      <c r="A141" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C141" s="14">
+        <v>40</v>
+      </c>
+      <c r="D141" s="14">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="25" customHeight="1">
+      <c r="A142" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C142" s="14">
+        <v>20</v>
+      </c>
+      <c r="D142" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="25" customHeight="1">
+      <c r="A143" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C143" s="14">
+        <v>20</v>
+      </c>
+      <c r="D143" s="14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6069,53 +6434,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="79" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="80" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="81" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6236,71 +6601,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="81" t="s">
+      <c r="F1" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="79" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="F2" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="82" t="s">
+      <c r="G2" s="80" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="F3" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="81" t="s">
         <v>136</v>
       </c>
     </row>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F403177-74A8-1847-ABB3-E3F19D921AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D78ADAE-E651-ED48-9973-559D79E0486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="170">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -544,6 +544,12 @@
   </si>
   <si>
     <t>Wyatt</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-23</t>
+  </si>
+  <si>
+    <t>Wednesday 9/23/26</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1483,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I22" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1494,7 +1500,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D143" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D153" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1937,7 +1943,7 @@
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -2018,7 +2024,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3796,7 +3802,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -4374,6 +4380,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="28">
+        <v>46288</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H22" s="63">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4387,7 +4419,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F21 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F22 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4404,7 +4436,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -6396,6 +6428,146 @@
       </c>
       <c r="D143" s="14">
         <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="25" customHeight="1">
+      <c r="A144" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C144" s="14">
+        <v>20</v>
+      </c>
+      <c r="D144" s="14">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="25" customHeight="1">
+      <c r="A145" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C145" s="14">
+        <v>20</v>
+      </c>
+      <c r="D145" s="14">
+        <v>44.75</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="25" customHeight="1">
+      <c r="A146" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C146" s="14">
+        <v>40</v>
+      </c>
+      <c r="D146" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="25" customHeight="1">
+      <c r="A147" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C147" s="14">
+        <v>50</v>
+      </c>
+      <c r="D147" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="25" customHeight="1">
+      <c r="A148" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C148" s="14">
+        <v>20</v>
+      </c>
+      <c r="D148" s="14">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="25" customHeight="1">
+      <c r="A149" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C149" s="14">
+        <v>20</v>
+      </c>
+      <c r="D149" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="25" customHeight="1">
+      <c r="A150" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C150" s="14">
+        <v>20</v>
+      </c>
+      <c r="D150" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="25" customHeight="1">
+      <c r="A151" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C151" s="14">
+        <v>40</v>
+      </c>
+      <c r="D151" s="14">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="25" customHeight="1">
+      <c r="A152" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C152" s="14">
+        <v>20</v>
+      </c>
+      <c r="D152" s="14">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="25" customHeight="1">
+      <c r="A153" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C153" s="14">
+        <v>20</v>
+      </c>
+      <c r="D153" s="14">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D78ADAE-E651-ED48-9973-559D79E0486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C59350B-F66F-4D4E-9FAB-F36647A38BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -543,13 +543,13 @@
     <t>Saturday 9/19/26</t>
   </si>
   <si>
-    <t>Wyatt</t>
-  </si>
-  <si>
     <t>cash-game-2026-09-23</t>
   </si>
   <si>
     <t>Wednesday 9/23/26</t>
+  </si>
+  <si>
+    <t>Wyatt T.</t>
   </si>
 </sst>
 </file>
@@ -4382,13 +4382,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="D22" s="28">
         <v>46288</v>
@@ -6197,7 +6197,7 @@
         <v>161</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C127" s="14">
         <v>40</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="144" spans="1:4" ht="25" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>46</v>
@@ -6446,7 +6446,7 @@
     </row>
     <row r="145" spans="1:4" ht="25" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>67</v>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="146" spans="1:4" ht="25" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>62</v>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="147" spans="1:4" ht="25" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>65</v>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="148" spans="1:4" ht="25" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>38</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="149" spans="1:4" ht="25" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>68</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="150" spans="1:4" ht="25" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>71</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="151" spans="1:4" ht="25" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>63</v>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="152" spans="1:4" ht="25" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>70</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="153" spans="1:4" ht="25" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>64</v>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C59350B-F66F-4D4E-9FAB-F36647A38BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9BC17B-B916-DE49-8C8D-67EE111387A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="172">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -550,6 +550,12 @@
   </si>
   <si>
     <t>Wyatt T.</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-26</t>
+  </si>
+  <si>
+    <t>Saturday 9/26/26</t>
   </si>
 </sst>
 </file>
@@ -1109,19 +1115,6 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1131,6 +1124,19 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1483,7 +1489,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I22" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I23" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1500,7 +1506,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D153" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D162" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1762,106 +1768,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="76" t="s">
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="71" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="76" t="s">
+      <c r="A2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="71" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="77" t="s">
+      <c r="E3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="77" t="s">
+      <c r="G3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="72" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="78" t="s">
+      <c r="D5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="78" t="s">
+      <c r="E5" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="73" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1869,22 +1875,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="75" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1896,22 +1902,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1923,49 +1929,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="75" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F9" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="77" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1977,22 +1983,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="75" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -2004,237 +2010,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="74" t="s">
+      <c r="F11" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="77" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
-        <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A500)</f>
-        <v>202</v>
+        <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A499)</f>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="75" t="s">
+      <c r="G14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="75" t="s">
+      <c r="H14" s="78" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="E15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="72" t="s">
+      <c r="H15" s="74" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="71" t="s">
+      <c r="E16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="71" t="s">
+      <c r="G16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="76" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="72" t="s">
+      <c r="A17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="74" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="71" t="s">
+      <c r="G18" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="76" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="72" t="s">
+      <c r="H19" s="74" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="71" t="s">
+      <c r="A20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="71" t="s">
+      <c r="E20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="71" t="s">
+      <c r="F20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="71" t="s">
+      <c r="G20" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="71" t="s">
+      <c r="H20" s="76" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3802,8 +3808,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
@@ -3818,7 +3824,7 @@
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20" customHeight="1">
+    <row r="1" spans="1:9" ht="19" customHeight="1">
       <c r="A1" s="79" t="s">
         <v>81</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20" customHeight="1">
+    <row r="2" spans="1:9" ht="19" customHeight="1">
       <c r="A2" s="80" t="s">
         <v>82</v>
       </c>
@@ -3876,7 +3882,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20" customHeight="1">
+    <row r="3" spans="1:9" ht="19" customHeight="1">
       <c r="A3" s="81" t="s">
         <v>26</v>
       </c>
@@ -3905,7 +3911,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="20" customHeight="1">
+    <row r="4" spans="1:9" ht="19" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
@@ -3934,7 +3940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20" customHeight="1">
+    <row r="5" spans="1:9" ht="19" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>84</v>
       </c>
@@ -3961,7 +3967,7 @@
       </c>
       <c r="I5" s="32"/>
     </row>
-    <row r="6" spans="1:9" ht="20" customHeight="1">
+    <row r="6" spans="1:9" ht="19" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>87</v>
       </c>
@@ -3988,7 +3994,7 @@
       </c>
       <c r="I6" s="33"/>
     </row>
-    <row r="7" spans="1:9" ht="20" customHeight="1">
+    <row r="7" spans="1:9" ht="19" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>89</v>
       </c>
@@ -4015,7 +4021,7 @@
       </c>
       <c r="I7" s="33"/>
     </row>
-    <row r="8" spans="1:9" ht="20" customHeight="1">
+    <row r="8" spans="1:9" ht="19" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>91</v>
       </c>
@@ -4042,7 +4048,7 @@
       </c>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="1:9" ht="20" customHeight="1">
+    <row r="9" spans="1:9" ht="19" customHeight="1">
       <c r="A9" s="13" t="s">
         <v>93</v>
       </c>
@@ -4064,11 +4070,11 @@
       <c r="G9" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H9" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="20" customHeight="1">
+      <c r="H9" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19" customHeight="1">
       <c r="A10" s="13" t="s">
         <v>95</v>
       </c>
@@ -4090,11 +4096,11 @@
       <c r="G10" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H10" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="20" customHeight="1">
+      <c r="H10" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>97</v>
       </c>
@@ -4116,11 +4122,11 @@
       <c r="G11" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H11" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="20" customHeight="1">
+      <c r="H11" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>99</v>
       </c>
@@ -4142,11 +4148,11 @@
       <c r="G12" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H12" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="20" customHeight="1">
+      <c r="H12" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>101</v>
       </c>
@@ -4168,11 +4174,11 @@
       <c r="G13" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H13" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="20" customHeight="1">
+      <c r="H13" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>103</v>
       </c>
@@ -4194,11 +4200,11 @@
       <c r="G14" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H14" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="20" customHeight="1">
+      <c r="H14" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="19" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>105</v>
       </c>
@@ -4220,11 +4226,11 @@
       <c r="G15" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H15" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="20" customHeight="1">
+      <c r="H15" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="19" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>107</v>
       </c>
@@ -4246,11 +4252,11 @@
       <c r="G16" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H16" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="H16" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="19" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -4272,11 +4278,11 @@
       <c r="G17" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H17" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="H17" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="19" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>159</v>
       </c>
@@ -4298,11 +4304,11 @@
       <c r="G18" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H18" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="H18" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="19" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>161</v>
       </c>
@@ -4324,11 +4330,11 @@
       <c r="G19" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H19" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="H19" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="19" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>162</v>
       </c>
@@ -4350,11 +4356,11 @@
       <c r="G20" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H20" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="H20" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="19" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>165</v>
       </c>
@@ -4376,11 +4382,11 @@
       <c r="G21" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H21" s="63">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="H21" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="19" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>167</v>
       </c>
@@ -4402,7 +4408,33 @@
       <c r="G22" s="65">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H22" s="63">
+      <c r="H22" s="64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="19" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="28">
+        <v>46291</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H23" s="64">
         <v>20</v>
       </c>
     </row>
@@ -4419,7 +4451,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F22 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F23 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4436,7 +4468,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -6570,6 +6602,132 @@
         <v>35</v>
       </c>
     </row>
+    <row r="154" spans="1:4" ht="25" customHeight="1">
+      <c r="A154" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C154" s="14">
+        <v>20</v>
+      </c>
+      <c r="D154" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="25" customHeight="1">
+      <c r="A155" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C155" s="14">
+        <v>40</v>
+      </c>
+      <c r="D155" s="14">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="25" customHeight="1">
+      <c r="A156" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C156" s="14">
+        <v>20</v>
+      </c>
+      <c r="D156" s="14">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="25" customHeight="1">
+      <c r="A157" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C157" s="14">
+        <v>40</v>
+      </c>
+      <c r="D157" s="14">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="25" customHeight="1">
+      <c r="A158" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C158" s="14">
+        <v>20</v>
+      </c>
+      <c r="D158" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="25" customHeight="1">
+      <c r="A159" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C159" s="14">
+        <v>40</v>
+      </c>
+      <c r="D159" s="14">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="25" customHeight="1">
+      <c r="A160" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C160" s="14">
+        <v>20</v>
+      </c>
+      <c r="D160" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="25" customHeight="1">
+      <c r="A161" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C161" s="14">
+        <v>20</v>
+      </c>
+      <c r="D161" s="14">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="25" customHeight="1">
+      <c r="A162" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C162" s="14">
+        <v>20</v>
+      </c>
+      <c r="D162" s="14">
+        <v>51.6</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
@@ -6577,11 +6735,11 @@
     <mergeCell ref="A3:D3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="whole" sqref="C5:C459" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="whole" sqref="C5:C458" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="D5:D459" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="whole" sqref="D5:D458" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9BC17B-B916-DE49-8C8D-67EE111387A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB22884-6278-6240-9CC4-3BDB9B79DBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="174">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -556,13 +556,20 @@
   </si>
   <si>
     <t>Saturday 9/26/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-09-30</t>
+  </si>
+  <si>
+    <t>Wednesday 9/30/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
@@ -937,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1160,6 +1167,7 @@
     <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1489,7 +1497,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I23" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I24" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1506,7 +1514,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D162" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D171" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1949,7 +1957,7 @@
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -2030,7 +2038,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3808,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -4438,6 +4446,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="24" spans="1:8" ht="19" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="28">
+        <v>46295</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H24" s="88">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4451,7 +4485,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F23 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F24 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4468,7 +4502,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -6726,6 +6760,132 @@
       </c>
       <c r="D162" s="14">
         <v>51.6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="25" customHeight="1">
+      <c r="A163" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C163" s="14">
+        <v>20</v>
+      </c>
+      <c r="D163" s="14">
+        <v>64.75</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="25" customHeight="1">
+      <c r="A164" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C164" s="14">
+        <v>20</v>
+      </c>
+      <c r="D164" s="14">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="25" customHeight="1">
+      <c r="A165" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C165" s="14">
+        <v>80</v>
+      </c>
+      <c r="D165" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="25" customHeight="1">
+      <c r="A166" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C166" s="14">
+        <v>60</v>
+      </c>
+      <c r="D166" s="14">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="25" customHeight="1">
+      <c r="A167" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C167" s="14">
+        <v>40</v>
+      </c>
+      <c r="D167" s="14">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="25" customHeight="1">
+      <c r="A168" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C168" s="14">
+        <v>20</v>
+      </c>
+      <c r="D168" s="14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="25" customHeight="1">
+      <c r="A169" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C169" s="14">
+        <v>20</v>
+      </c>
+      <c r="D169" s="14">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="25" customHeight="1">
+      <c r="A170" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C170" s="14">
+        <v>60</v>
+      </c>
+      <c r="D170" s="14">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="25" customHeight="1">
+      <c r="A171" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C171" s="14">
+        <v>40</v>
+      </c>
+      <c r="D171" s="14">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB22884-6278-6240-9CC4-3BDB9B79DBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EF5C10-8F7E-6343-8AF2-855B1AA75764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="176">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -562,6 +562,12 @@
   </si>
   <si>
     <t>Wednesday 9/30/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-10-03</t>
+  </si>
+  <si>
+    <t>Saturday 10/3/26</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1503,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I24" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I25" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1514,7 +1520,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D171" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D178" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1957,7 +1963,7 @@
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -2038,7 +2044,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3816,7 +3822,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -4472,6 +4478,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="25" spans="1:8" ht="19" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="28">
+        <v>46298</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H25" s="88">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4485,7 +4517,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F24 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F25 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4502,7 +4534,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -6886,6 +6918,104 @@
       </c>
       <c r="D171" s="14">
         <v>44</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="25" customHeight="1">
+      <c r="A172" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C172" s="14">
+        <v>20</v>
+      </c>
+      <c r="D172" s="14">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="25" customHeight="1">
+      <c r="A173" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C173" s="14">
+        <v>40</v>
+      </c>
+      <c r="D173" s="14">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="25" customHeight="1">
+      <c r="A174" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C174" s="14">
+        <v>20</v>
+      </c>
+      <c r="D174" s="14">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="25" customHeight="1">
+      <c r="A175" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C175" s="14">
+        <v>40</v>
+      </c>
+      <c r="D175" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="25" customHeight="1">
+      <c r="A176" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C176" s="14">
+        <v>20</v>
+      </c>
+      <c r="D176" s="14">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="25" customHeight="1">
+      <c r="A177" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C177" s="14">
+        <v>20</v>
+      </c>
+      <c r="D177" s="14">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="25" customHeight="1">
+      <c r="A178" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C178" s="14">
+        <v>40</v>
+      </c>
+      <c r="D178" s="14">
+        <v>54.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EF5C10-8F7E-6343-8AF2-855B1AA75764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95623EA-0F29-2546-AB55-FC3E4A7B9CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="175">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -183,9 +183,6 @@
     <t>Matt O.</t>
   </si>
   <si>
-    <t>upcoming</t>
-  </si>
-  <si>
     <t>TOURNAMENT RESULTS</t>
   </si>
   <si>
@@ -438,12 +435,6 @@
     <t>August 2026 tournament winner: Nathan C.</t>
   </si>
   <si>
-    <t>/photos/luck-casino.avif</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>ANNOUNCEMENTS</t>
   </si>
   <si>
@@ -568,6 +559,12 @@
   </si>
   <si>
     <t>Saturday 10/3/26</t>
+  </si>
+  <si>
+    <t>/photos/october2026tourney.heic</t>
+  </si>
+  <si>
+    <t>October 2026 tournament winner: Adam B.</t>
   </si>
 </sst>
 </file>
@@ -950,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1074,15 +1071,6 @@
     <xf numFmtId="164" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="18" fontId="12" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1119,6 +1107,7 @@
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1128,6 +1117,19 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1137,19 +1139,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1173,7 +1162,17 @@
     <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="12" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1220,6 +1219,15 @@
           <bgColor rgb="FFE5E7EB"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1412,14 +1420,6 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
@@ -1486,7 +1486,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I57" totalsRowShown="0" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I56" totalsRowShown="0" dataDxfId="23">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="21"/>
@@ -1494,9 +1494,9 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="19"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="18"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1538,7 +1538,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EventPhotosTable" displayName="EventPhotosTable" ref="A4:E8" totalsRowShown="0">
   <autoFilter ref="A4:E8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Image Path"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Caption"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Show on Home"/>
@@ -1549,25 +1549,25 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A4:G7" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Date" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Title" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Body" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Date" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Title" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Body" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="BlindSchedulesTable" displayName="BlindSchedulesTable" ref="A4:E38" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="BlindSchedulesTable" displayName="BlindSchedulesTable" ref="A4:E37" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Level"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Duration"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Small Blind"/>
@@ -1782,106 +1782,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="71" t="s">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="74" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="71" t="s">
+      <c r="A2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="74" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="75" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="76" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1889,22 +1889,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="74" t="s">
+      <c r="E6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="71" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1916,49 +1916,49 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="77" t="s">
+      <c r="G7" s="72" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
         <f>COUNTIF(Tournaments!F5:F500,"upcoming")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="75" t="s">
+      <c r="G8" s="71" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
@@ -1970,22 +1970,22 @@
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="76" t="s">
+      <c r="C9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="72" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1997,22 +1997,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="74" t="s">
+      <c r="E10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="75" t="s">
+      <c r="F10" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="75" t="s">
+      <c r="G10" s="71" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -2024,237 +2024,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="77" t="s">
+      <c r="G11" s="72" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
-        <f>COUNTA('Tournament Results'!A5:A511)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>227</v>
+        <f>COUNTA('Tournament Results'!A5:A509)+COUNTA('Cash Game Results'!A5:A499)</f>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="78" t="s">
+      <c r="G14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="73" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="74" t="s">
+      <c r="E15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="74" t="s">
+      <c r="F15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="74" t="s">
+      <c r="H15" s="70" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="76" t="s">
+      <c r="E16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="76" t="s">
+      <c r="G16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="76" t="s">
+      <c r="H16" s="69" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="74" t="s">
+      <c r="A17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="70" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="76" t="s">
+      <c r="A18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="76" t="s">
+      <c r="G18" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="74" t="s">
+      <c r="A19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="74" t="s">
+      <c r="E19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="74" t="s">
+      <c r="F19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="74" t="s">
+      <c r="G19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="74" t="s">
+      <c r="H19" s="70" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="76" t="s">
+      <c r="E20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="76" t="s">
+      <c r="G20" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="76" t="s">
+      <c r="H20" s="69" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2279,89 +2279,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="77" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="78" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="79" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2413,8 +2413,8 @@
       <c r="F5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="61">
+      <c r="G5" s="62"/>
+      <c r="H5" s="58">
         <v>20</v>
       </c>
       <c r="I5" s="9"/>
@@ -2438,8 +2438,8 @@
       <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="65"/>
-      <c r="H6" s="62">
+      <c r="G6" s="62"/>
+      <c r="H6" s="59">
         <v>20</v>
       </c>
     </row>
@@ -2462,10 +2462,10 @@
       <c r="F7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="62">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H7" s="63">
+      <c r="H7" s="60">
         <v>20</v>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="65">
+        <v>39</v>
+      </c>
+      <c r="G8" s="62">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H8" s="63">
+      <c r="H8" s="60">
         <v>50</v>
       </c>
     </row>
@@ -2525,8 +2525,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="28" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
@@ -2540,86 +2540,86 @@
     <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:9" ht="28" customHeight="1">
+      <c r="A1" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+    </row>
+    <row r="2" spans="1:9" ht="28" customHeight="1">
+      <c r="A2" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-    </row>
-    <row r="2" spans="1:9" ht="27" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+    </row>
+    <row r="3" spans="1:9" ht="28" customHeight="1">
+      <c r="A3" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-    </row>
-    <row r="3" spans="1:9" ht="27" customHeight="1">
-      <c r="A3" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-    </row>
-    <row r="4" spans="1:9" ht="27" customHeight="1">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+    </row>
+    <row r="4" spans="1:9" ht="28" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F4" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="G4" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="I4" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="27" customHeight="1">
+    </row>
+    <row r="5" spans="1:9" ht="28" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="20">
         <v>40</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="44">
         <v>100</v>
@@ -2627,22 +2627,22 @@
       <c r="F5" s="44">
         <v>0</v>
       </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="51"/>
-    </row>
-    <row r="6" spans="1:9" ht="27" customHeight="1">
+      <c r="G5" s="87"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="48"/>
+    </row>
+    <row r="6" spans="1:9" ht="28" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="22">
         <v>20</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="45">
         <v>100</v>
@@ -2650,22 +2650,22 @@
       <c r="F6" s="45">
         <v>0</v>
       </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="53"/>
-    </row>
-    <row r="7" spans="1:9" ht="27" customHeight="1">
+      <c r="G6" s="88"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="50"/>
+    </row>
+    <row r="7" spans="1:9" ht="28" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="14">
         <v>40</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="46">
         <v>100</v>
@@ -2673,11 +2673,11 @@
       <c r="F7" s="46">
         <v>0</v>
       </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="55"/>
-    </row>
-    <row r="8" spans="1:9" ht="27" customHeight="1">
+      <c r="G7" s="89"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="52"/>
+    </row>
+    <row r="8" spans="1:9" ht="28" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="45">
         <v>100</v>
@@ -2696,16 +2696,16 @@
       <c r="F8" s="45">
         <v>0</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="53"/>
-    </row>
-    <row r="9" spans="1:9" ht="27" customHeight="1">
+      <c r="G8" s="88"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
+    </row>
+    <row r="9" spans="1:9" ht="28" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
@@ -2719,16 +2719,16 @@
       <c r="F9" s="46">
         <v>0</v>
       </c>
-      <c r="G9" s="49"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="55"/>
-    </row>
-    <row r="10" spans="1:9" ht="27" customHeight="1">
+      <c r="G9" s="89"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="52"/>
+    </row>
+    <row r="10" spans="1:9" ht="28" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" s="14">
         <v>20</v>
@@ -2742,16 +2742,16 @@
       <c r="F10" s="45">
         <v>0</v>
       </c>
-      <c r="G10" s="48"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="53"/>
-    </row>
-    <row r="11" spans="1:9" ht="27" customHeight="1">
+      <c r="G10" s="88"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="50"/>
+    </row>
+    <row r="11" spans="1:9" ht="28" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="14">
         <v>20</v>
@@ -2765,16 +2765,16 @@
       <c r="F11" s="46">
         <v>0</v>
       </c>
-      <c r="G11" s="49"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="55"/>
-    </row>
-    <row r="12" spans="1:9" ht="27" customHeight="1">
+      <c r="G11" s="89"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="52"/>
+    </row>
+    <row r="12" spans="1:9" ht="28" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" s="14">
         <v>40</v>
@@ -2788,16 +2788,16 @@
       <c r="F12" s="45">
         <v>0</v>
       </c>
-      <c r="G12" s="48"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="53"/>
-    </row>
-    <row r="13" spans="1:9" ht="27" customHeight="1">
+      <c r="G12" s="88"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+    </row>
+    <row r="13" spans="1:9" ht="28" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" s="14">
         <v>20</v>
@@ -2811,16 +2811,16 @@
       <c r="F13" s="46">
         <v>0</v>
       </c>
-      <c r="G13" s="49"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="55"/>
-    </row>
-    <row r="14" spans="1:9" ht="27" customHeight="1">
+      <c r="G13" s="89"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="52"/>
+    </row>
+    <row r="14" spans="1:9" ht="28" customHeight="1">
       <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="14">
         <v>20</v>
@@ -2834,16 +2834,16 @@
       <c r="F14" s="45">
         <v>0</v>
       </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="53"/>
-    </row>
-    <row r="15" spans="1:9" ht="27" customHeight="1">
+      <c r="G14" s="88"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="50"/>
+    </row>
+    <row r="15" spans="1:9" ht="28" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" s="14">
         <v>20</v>
@@ -2857,11 +2857,11 @@
       <c r="F15" s="46">
         <v>0</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="55"/>
-    </row>
-    <row r="16" spans="1:9" ht="27" customHeight="1">
+      <c r="G15" s="89"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="52"/>
+    </row>
+    <row r="16" spans="1:9" ht="28" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
@@ -2880,16 +2880,16 @@
       <c r="F16" s="46">
         <v>0</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="55"/>
-    </row>
-    <row r="17" spans="1:9" ht="27" customHeight="1">
+      <c r="G16" s="89"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="52"/>
+    </row>
+    <row r="17" spans="1:9" ht="28" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="14">
         <v>20</v>
@@ -2903,16 +2903,16 @@
       <c r="F17" s="45">
         <v>0</v>
       </c>
-      <c r="G17" s="48"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="53"/>
-    </row>
-    <row r="18" spans="1:9" ht="27" customHeight="1">
+      <c r="G17" s="88"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="50"/>
+    </row>
+    <row r="18" spans="1:9" ht="28" customHeight="1">
       <c r="A18" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="14">
         <v>20</v>
@@ -2926,16 +2926,16 @@
       <c r="F18" s="46">
         <v>0</v>
       </c>
-      <c r="G18" s="49"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="55"/>
-    </row>
-    <row r="19" spans="1:9" ht="27" customHeight="1">
+      <c r="G18" s="89"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
+    </row>
+    <row r="19" spans="1:9" ht="28" customHeight="1">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="14">
         <v>20</v>
@@ -2949,16 +2949,16 @@
       <c r="F19" s="45">
         <v>0</v>
       </c>
-      <c r="G19" s="48"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="53"/>
-    </row>
-    <row r="20" spans="1:9" ht="27" customHeight="1">
+      <c r="G19" s="88"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="50"/>
+    </row>
+    <row r="20" spans="1:9" ht="28" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="14">
         <v>40</v>
@@ -2972,22 +2972,22 @@
       <c r="F20" s="46">
         <v>0</v>
       </c>
-      <c r="G20" s="49"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="55"/>
-    </row>
-    <row r="21" spans="1:9" ht="27" customHeight="1">
+      <c r="G20" s="89"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="52"/>
+    </row>
+    <row r="21" spans="1:9" ht="28" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="21">
         <v>60</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" s="45">
         <v>195</v>
@@ -2995,22 +2995,22 @@
       <c r="F21" s="45">
         <v>0</v>
       </c>
-      <c r="G21" s="48"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="53"/>
-    </row>
-    <row r="22" spans="1:9" ht="27" customHeight="1">
+      <c r="G21" s="88"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="50"/>
+    </row>
+    <row r="22" spans="1:9" ht="28" customHeight="1">
       <c r="A22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="21">
+        <v>20</v>
+      </c>
+      <c r="D22" s="24" t="s">
         <v>76</v>
-      </c>
-      <c r="C22" s="21">
-        <v>20</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>77</v>
       </c>
       <c r="E22" s="46">
         <v>87.75</v>
@@ -3018,11 +3018,11 @@
       <c r="F22" s="46">
         <v>0</v>
       </c>
-      <c r="G22" s="49"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="55"/>
-    </row>
-    <row r="23" spans="1:9" ht="27" customHeight="1">
+      <c r="G22" s="89"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="52"/>
+    </row>
+    <row r="23" spans="1:9" ht="28" customHeight="1">
       <c r="A23" s="13" t="s">
         <v>36</v>
       </c>
@@ -3041,16 +3041,16 @@
       <c r="F23" s="45">
         <v>0</v>
       </c>
-      <c r="G23" s="48"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="53"/>
-    </row>
-    <row r="24" spans="1:9" ht="27" customHeight="1">
+      <c r="G23" s="88"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="50"/>
+    </row>
+    <row r="24" spans="1:9" ht="28" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="14">
         <v>20</v>
@@ -3064,16 +3064,16 @@
       <c r="F24" s="46">
         <v>0</v>
       </c>
-      <c r="G24" s="49"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="55"/>
-    </row>
-    <row r="25" spans="1:9" ht="27" customHeight="1">
+      <c r="G24" s="89"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="52"/>
+    </row>
+    <row r="25" spans="1:9" ht="28" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="14">
         <v>20</v>
@@ -3087,16 +3087,16 @@
       <c r="F25" s="45">
         <v>0</v>
       </c>
-      <c r="G25" s="48"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="53"/>
-    </row>
-    <row r="26" spans="1:9" ht="27" customHeight="1">
+      <c r="G25" s="88"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="50"/>
+    </row>
+    <row r="26" spans="1:9" ht="28" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="14">
         <v>20</v>
@@ -3110,16 +3110,16 @@
       <c r="F26" s="46">
         <v>0</v>
       </c>
-      <c r="G26" s="49"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="55"/>
-    </row>
-    <row r="27" spans="1:9" ht="27" customHeight="1">
+      <c r="G26" s="89"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="52"/>
+    </row>
+    <row r="27" spans="1:9" ht="28" customHeight="1">
       <c r="A27" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C27" s="14">
         <v>20</v>
@@ -3133,16 +3133,16 @@
       <c r="F27" s="45">
         <v>0</v>
       </c>
-      <c r="G27" s="48"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-    </row>
-    <row r="28" spans="1:9" ht="27" customHeight="1">
+      <c r="G27" s="88"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="50"/>
+    </row>
+    <row r="28" spans="1:9" ht="28" customHeight="1">
       <c r="A28" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="14">
         <v>20</v>
@@ -3156,16 +3156,16 @@
       <c r="F28" s="46">
         <v>0</v>
       </c>
-      <c r="G28" s="49"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="55"/>
-    </row>
-    <row r="29" spans="1:9" ht="27" customHeight="1">
+      <c r="G28" s="89"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="52"/>
+    </row>
+    <row r="29" spans="1:9" ht="28" customHeight="1">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -3179,16 +3179,16 @@
       <c r="F29" s="45">
         <v>0</v>
       </c>
-      <c r="G29" s="48"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="53"/>
-    </row>
-    <row r="30" spans="1:9" ht="27" customHeight="1">
+      <c r="G29" s="88"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="50"/>
+    </row>
+    <row r="30" spans="1:9" ht="28" customHeight="1">
       <c r="A30" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="14">
         <v>30</v>
@@ -3202,11 +3202,11 @@
       <c r="F30" s="46">
         <v>0</v>
       </c>
-      <c r="G30" s="49"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="55"/>
-    </row>
-    <row r="31" spans="1:9" ht="27" customHeight="1">
+      <c r="G30" s="89"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="52"/>
+    </row>
+    <row r="31" spans="1:9" ht="28" customHeight="1">
       <c r="A31" s="13" t="s">
         <v>36</v>
       </c>
@@ -3225,16 +3225,16 @@
       <c r="F31" s="45">
         <v>0</v>
       </c>
-      <c r="G31" s="48"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53"/>
-    </row>
-    <row r="32" spans="1:9" ht="27" customHeight="1">
+      <c r="G31" s="88"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50"/>
+    </row>
+    <row r="32" spans="1:9" ht="28" customHeight="1">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="14">
         <v>40</v>
@@ -3248,16 +3248,16 @@
       <c r="F32" s="46">
         <v>0</v>
       </c>
-      <c r="G32" s="49"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="55"/>
-    </row>
-    <row r="33" spans="1:9" ht="27" customHeight="1">
+      <c r="G32" s="89"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="52"/>
+    </row>
+    <row r="33" spans="1:9" ht="28" customHeight="1">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -3271,16 +3271,16 @@
       <c r="F33" s="45">
         <v>0</v>
       </c>
-      <c r="G33" s="48"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="53"/>
-    </row>
-    <row r="34" spans="1:9" ht="27" customHeight="1">
+      <c r="G33" s="88"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50"/>
+    </row>
+    <row r="34" spans="1:9" ht="28" customHeight="1">
       <c r="A34" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34" s="14">
         <v>40</v>
@@ -3294,16 +3294,16 @@
       <c r="F34" s="46">
         <v>0</v>
       </c>
-      <c r="G34" s="49"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="55"/>
-    </row>
-    <row r="35" spans="1:9" ht="27" customHeight="1">
+      <c r="G34" s="89"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="52"/>
+    </row>
+    <row r="35" spans="1:9" ht="28" customHeight="1">
       <c r="A35" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35" s="14">
         <v>40</v>
@@ -3317,22 +3317,22 @@
       <c r="F35" s="45">
         <v>0</v>
       </c>
-      <c r="G35" s="48">
+      <c r="G35" s="88">
         <v>4</v>
       </c>
-      <c r="H35" s="52">
+      <c r="H35" s="49">
         <v>0.84375</v>
       </c>
-      <c r="I35" s="53" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="27" customHeight="1">
+      <c r="I35" s="50" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28" customHeight="1">
       <c r="A36" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C36" s="14">
         <v>20</v>
@@ -3346,17 +3346,17 @@
       <c r="F36" s="46">
         <v>0</v>
       </c>
-      <c r="G36" s="49">
+      <c r="G36" s="89">
         <v>5</v>
       </c>
-      <c r="H36" s="54">
+      <c r="H36" s="51">
         <v>0.85069444444444442</v>
       </c>
-      <c r="I36" s="55" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="27" customHeight="1">
+      <c r="I36" s="52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28" customHeight="1">
       <c r="A37" s="13" t="s">
         <v>42</v>
       </c>
@@ -3375,22 +3375,22 @@
       <c r="F37" s="45">
         <v>0</v>
       </c>
-      <c r="G37" s="48">
+      <c r="G37" s="88">
         <v>5</v>
       </c>
-      <c r="H37" s="52">
+      <c r="H37" s="49">
         <v>0.85624999999999996</v>
       </c>
-      <c r="I37" s="53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="27" customHeight="1">
+      <c r="I37" s="50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28" customHeight="1">
       <c r="A38" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="14">
         <v>40</v>
@@ -3404,22 +3404,22 @@
       <c r="F38" s="46">
         <v>0</v>
       </c>
-      <c r="G38" s="49">
+      <c r="G38" s="89">
         <v>6</v>
       </c>
-      <c r="H38" s="54">
+      <c r="H38" s="51">
         <v>0.87083333333333335</v>
       </c>
-      <c r="I38" s="55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="27" customHeight="1">
+      <c r="I38" s="52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="28" customHeight="1">
       <c r="A39" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="14">
         <v>40</v>
@@ -3433,22 +3433,22 @@
       <c r="F39" s="45">
         <v>0</v>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="88">
         <v>6</v>
       </c>
-      <c r="H39" s="52">
+      <c r="H39" s="49">
         <v>0.87430555555555556</v>
       </c>
-      <c r="I39" s="53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="27" customHeight="1">
+      <c r="I39" s="50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>
@@ -3462,22 +3462,22 @@
       <c r="F40" s="46">
         <v>0</v>
       </c>
-      <c r="G40" s="49">
+      <c r="G40" s="89">
         <v>6</v>
       </c>
-      <c r="H40" s="54">
+      <c r="H40" s="51">
         <v>0.87986111111111109</v>
       </c>
-      <c r="I40" s="55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="27" customHeight="1">
+      <c r="I40" s="52" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C41" s="14">
         <v>60</v>
@@ -3491,17 +3491,17 @@
       <c r="F41" s="45">
         <v>0</v>
       </c>
-      <c r="G41" s="48">
+      <c r="G41" s="88">
         <v>6</v>
       </c>
-      <c r="H41" s="52">
+      <c r="H41" s="49">
         <v>0.88263888888888886</v>
       </c>
-      <c r="I41" s="53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="27" customHeight="1">
+      <c r="I41" s="50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="28" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>42</v>
       </c>
@@ -3520,22 +3520,22 @@
       <c r="F42" s="46">
         <v>0</v>
       </c>
-      <c r="G42" s="49">
+      <c r="G42" s="89">
         <v>7</v>
       </c>
-      <c r="H42" s="54">
+      <c r="H42" s="51">
         <v>0.89583333333333337</v>
       </c>
-      <c r="I42" s="55" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="27" customHeight="1">
+      <c r="I42" s="52" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="28" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="14">
         <v>40</v>
@@ -3549,22 +3549,22 @@
       <c r="F43" s="45">
         <v>0</v>
       </c>
-      <c r="G43" s="48">
+      <c r="G43" s="88">
         <v>9</v>
       </c>
-      <c r="H43" s="52">
+      <c r="H43" s="49">
         <v>0.92013888888888884</v>
       </c>
-      <c r="I43" s="53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="27" customHeight="1">
+      <c r="I43" s="50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C44" s="14">
         <v>20</v>
@@ -3578,22 +3578,22 @@
       <c r="F44" s="46">
         <v>0</v>
       </c>
-      <c r="G44" s="49">
+      <c r="G44" s="89">
         <v>10</v>
       </c>
-      <c r="H44" s="54">
+      <c r="H44" s="51">
         <v>0.93055555555555558</v>
       </c>
-      <c r="I44" s="55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="27" customHeight="1">
+      <c r="I44" s="52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="28" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="14">
         <v>60</v>
@@ -3607,22 +3607,22 @@
       <c r="F45" s="45">
         <v>0</v>
       </c>
-      <c r="G45" s="48">
+      <c r="G45" s="88">
         <v>11</v>
       </c>
-      <c r="H45" s="52">
+      <c r="H45" s="49">
         <v>0.95138888888888884</v>
       </c>
-      <c r="I45" s="53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="27" customHeight="1">
+      <c r="I45" s="50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="28" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" s="14">
         <v>20</v>
@@ -3636,22 +3636,22 @@
       <c r="F46" s="46">
         <v>0</v>
       </c>
-      <c r="G46" s="49">
+      <c r="G46" s="89">
         <v>12</v>
       </c>
-      <c r="H46" s="54">
+      <c r="H46" s="51">
         <v>0.95625000000000004</v>
       </c>
-      <c r="I46" s="55" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="27" customHeight="1">
+      <c r="I46" s="52" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="28" customHeight="1">
       <c r="A47" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C47" s="14">
         <v>20</v>
@@ -3665,22 +3665,22 @@
       <c r="F47" s="45">
         <v>0</v>
       </c>
-      <c r="G47" s="48">
+      <c r="G47" s="88">
         <v>13</v>
       </c>
-      <c r="H47" s="52">
+      <c r="H47" s="49">
         <v>0.96736111111111112</v>
       </c>
-      <c r="I47" s="53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="27" customHeight="1">
+      <c r="I47" s="50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28" customHeight="1">
       <c r="A48" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C48" s="14">
         <v>20</v>
@@ -3694,11 +3694,11 @@
       <c r="F48" s="46">
         <v>0</v>
       </c>
-      <c r="G48" s="49"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="55"/>
-    </row>
-    <row r="49" spans="1:3" ht="27" customHeight="1">
+      <c r="G48" s="89"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="52"/>
+    </row>
+    <row r="49" spans="1:8" ht="28" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>44</v>
       </c>
@@ -3708,93 +3708,197 @@
       <c r="C49" s="14">
         <v>50</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="27" customHeight="1">
+      <c r="D49" s="16">
+        <v>8</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="90">
+        <v>4</v>
+      </c>
+      <c r="H49" s="86">
+        <v>0.86875000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="28" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="14">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="27" customHeight="1">
+      <c r="D50" s="16">
+        <v>6</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="90">
+        <v>5</v>
+      </c>
+      <c r="H50" s="86">
+        <v>0.88194444444444442</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="28" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C51" s="14">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="27" customHeight="1">
+      <c r="D51" s="16">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
+        <v>375</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="90"/>
+    </row>
+    <row r="52" spans="1:8" ht="28" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C52" s="14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="27" customHeight="1">
+        <v>225</v>
+      </c>
+      <c r="D52" s="16">
+        <v>5</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="90">
+        <v>6</v>
+      </c>
+      <c r="H52" s="86">
+        <v>0.8930555555555556</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="28" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C53" s="14">
         <v>50</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="27" customHeight="1">
+      <c r="D53" s="16">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="90">
+        <v>11</v>
+      </c>
+      <c r="H53" s="86">
+        <v>0.96388888888888891</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="28" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C54" s="14">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="27" customHeight="1">
+      <c r="D54" s="16">
+        <v>2</v>
+      </c>
+      <c r="E54" s="1">
+        <v>187.5</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="90">
+        <v>12</v>
+      </c>
+      <c r="H54" s="86">
+        <v>0.97847222222222219</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="28" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C55" s="14">
         <v>50</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="27" customHeight="1">
+      <c r="D55" s="16">
+        <v>7</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="90">
+        <v>5</v>
+      </c>
+      <c r="H55" s="86">
+        <v>0.87847222222222221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="28" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C56" s="14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="27" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="14">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="D56" s="16">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="90">
+        <v>8</v>
+      </c>
+      <c r="H56" s="86">
+        <v>0.92986111111111114</v>
       </c>
     </row>
   </sheetData>
@@ -3804,11 +3908,11 @@
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="whole" sqref="C5:C459" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="whole" sqref="C5:C457" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="F5:G459" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="whole" sqref="F5:G457" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
@@ -3839,95 +3943,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="77" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19" customHeight="1">
+      <c r="A2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H2" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I2" s="78" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19" customHeight="1">
-      <c r="A2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="80" t="s">
-        <v>82</v>
-      </c>
-    </row>
     <row r="3" spans="1:9" ht="19" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="81" t="s">
+      <c r="F3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="81" t="s">
+      <c r="G3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="19" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
@@ -3956,13 +4060,13 @@
     </row>
     <row r="5" spans="1:9" ht="19" customHeight="1">
       <c r="A5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="D5" s="26">
         <v>46218</v>
@@ -3973,23 +4077,23 @@
       <c r="F5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="61">
+      <c r="G5" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="58">
         <v>20</v>
       </c>
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="19" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>87</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>88</v>
       </c>
       <c r="D6" s="35">
         <v>46221</v>
@@ -4000,23 +4104,23 @@
       <c r="F6" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H6" s="64">
+      <c r="H6" s="61">
         <v>20</v>
       </c>
       <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:9" ht="19" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="D7" s="35">
         <v>46225</v>
@@ -4027,23 +4131,23 @@
       <c r="F7" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="61">
         <v>20</v>
       </c>
       <c r="I7" s="33"/>
     </row>
     <row r="8" spans="1:9" ht="19" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="D8" s="35">
         <v>46232</v>
@@ -4054,23 +4158,23 @@
       <c r="F8" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H8" s="64">
+      <c r="H8" s="61">
         <v>20</v>
       </c>
       <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" ht="19" customHeight="1">
       <c r="A9" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="D9" s="28">
         <v>46239</v>
@@ -4081,22 +4185,22 @@
       <c r="F9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="65">
+      <c r="G9" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19" customHeight="1">
       <c r="A10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="D10" s="28">
         <v>46242</v>
@@ -4107,48 +4211,48 @@
       <c r="F10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="65">
+      <c r="G10" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H10" s="64">
+      <c r="H10" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="19" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D11" s="28">
         <v>46246</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="65">
+      <c r="G11" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="19" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="D12" s="28">
         <v>46249</v>
@@ -4159,22 +4263,22 @@
       <c r="F12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H12" s="64">
+      <c r="H12" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="19" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="D13" s="28">
         <v>46253</v>
@@ -4185,22 +4289,22 @@
       <c r="F13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="65">
+      <c r="G13" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="19" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="D14" s="28">
         <v>46256</v>
@@ -4211,22 +4315,22 @@
       <c r="F14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="65">
+      <c r="G14" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H14" s="64">
+      <c r="H14" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="19" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="D15" s="28">
         <v>46260</v>
@@ -4237,22 +4341,22 @@
       <c r="F15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="65">
+      <c r="G15" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H15" s="64">
+      <c r="H15" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="19" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="D16" s="28">
         <v>46263</v>
@@ -4263,22 +4367,22 @@
       <c r="F16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="65">
+      <c r="G16" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H16" s="64">
+      <c r="H16" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="19" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D17" s="28">
         <v>46267</v>
@@ -4289,22 +4393,22 @@
       <c r="F17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="65">
+      <c r="G17" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H17" s="64">
+      <c r="H17" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="19" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D18" s="28">
         <v>46275</v>
@@ -4315,74 +4419,74 @@
       <c r="F18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="65">
+      <c r="G18" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H18" s="64">
+      <c r="H18" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="19" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D19" s="28">
         <v>46277</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="65">
+      <c r="G19" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H19" s="64">
+      <c r="H19" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="19" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D20" s="28">
         <v>46281</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="65">
+      <c r="G20" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H20" s="64">
+      <c r="H20" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D21" s="28">
         <v>46284</v>
@@ -4393,22 +4497,22 @@
       <c r="F21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="65">
+      <c r="G21" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H21" s="64">
+      <c r="H21" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="19" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D22" s="28">
         <v>46288</v>
@@ -4419,22 +4523,22 @@
       <c r="F22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="65">
+      <c r="G22" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H22" s="64">
+      <c r="H22" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D23" s="28">
         <v>46291</v>
@@ -4445,22 +4549,22 @@
       <c r="F23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="65">
+      <c r="G23" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H23" s="64">
+      <c r="H23" s="61">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="19" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D24" s="28">
         <v>46295</v>
@@ -4471,22 +4575,22 @@
       <c r="F24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="65">
+      <c r="G24" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H24" s="88">
+      <c r="H24" s="65">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="19" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D25" s="28">
         <v>46298</v>
@@ -4497,10 +4601,10 @@
       <c r="F25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="65">
+      <c r="G25" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H25" s="88">
+      <c r="H25" s="65">
         <v>20</v>
       </c>
     </row>
@@ -4545,46 +4649,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-    </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-    </row>
-    <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>46</v>
@@ -4598,10 +4702,10 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="11">
         <v>40</v>
@@ -4612,10 +4716,10 @@
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="11">
         <v>20</v>
@@ -4626,10 +4730,10 @@
     </row>
     <row r="8" spans="1:4" ht="25" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="11">
         <v>40</v>
@@ -4640,10 +4744,10 @@
     </row>
     <row r="9" spans="1:4" ht="25" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="11">
         <v>60</v>
@@ -4654,10 +4758,10 @@
     </row>
     <row r="10" spans="1:4" ht="25" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="11">
         <v>60</v>
@@ -4668,7 +4772,7 @@
     </row>
     <row r="11" spans="1:4" ht="25" customHeight="1">
       <c r="A11" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>38</v>
@@ -4682,10 +4786,10 @@
     </row>
     <row r="12" spans="1:4" ht="25" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="14">
         <v>20</v>
@@ -4696,10 +4800,10 @@
     </row>
     <row r="13" spans="1:4" ht="25" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="14">
         <v>20</v>
@@ -4710,7 +4814,7 @@
     </row>
     <row r="14" spans="1:4" ht="25" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>38</v>
@@ -4724,10 +4828,10 @@
     </row>
     <row r="15" spans="1:4" ht="25" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="14">
         <v>100</v>
@@ -4738,10 +4842,10 @@
     </row>
     <row r="16" spans="1:4" ht="25" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4752,7 +4856,7 @@
     </row>
     <row r="17" spans="1:4" ht="25" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>46</v>
@@ -4766,10 +4870,10 @@
     </row>
     <row r="18" spans="1:4" ht="25" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="14">
         <v>20</v>
@@ -4780,10 +4884,10 @@
     </row>
     <row r="19" spans="1:4" ht="25" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="14">
         <v>20</v>
@@ -4794,10 +4898,10 @@
     </row>
     <row r="20" spans="1:4" ht="25" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="14">
         <v>60</v>
@@ -4808,10 +4912,10 @@
     </row>
     <row r="21" spans="1:4" ht="25" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="14">
         <v>120</v>
@@ -4822,7 +4926,7 @@
     </row>
     <row r="22" spans="1:4" ht="25" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>46</v>
@@ -4836,10 +4940,10 @@
     </row>
     <row r="23" spans="1:4" ht="25" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="14">
         <v>60</v>
@@ -4850,10 +4954,10 @@
     </row>
     <row r="24" spans="1:4" ht="25" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="14">
         <v>20</v>
@@ -4864,10 +4968,10 @@
     </row>
     <row r="25" spans="1:4" ht="25" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="14">
         <v>100</v>
@@ -4878,10 +4982,10 @@
     </row>
     <row r="26" spans="1:4" ht="25" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="14">
         <v>40</v>
@@ -4892,7 +4996,7 @@
     </row>
     <row r="27" spans="1:4" ht="25" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>38</v>
@@ -4906,10 +5010,10 @@
     </row>
     <row r="28" spans="1:4" ht="25" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" s="14">
         <v>20</v>
@@ -4920,10 +5024,10 @@
     </row>
     <row r="29" spans="1:4" ht="25" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -4934,10 +5038,10 @@
     </row>
     <row r="30" spans="1:4" ht="25" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="14">
         <v>20</v>
@@ -4948,7 +5052,7 @@
     </row>
     <row r="31" spans="1:4" ht="25" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>46</v>
@@ -4962,10 +5066,10 @@
     </row>
     <row r="32" spans="1:4" ht="25" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="14">
         <v>30</v>
@@ -4976,10 +5080,10 @@
     </row>
     <row r="33" spans="1:4" ht="25" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="14">
         <v>60</v>
@@ -4990,10 +5094,10 @@
     </row>
     <row r="34" spans="1:4" ht="25" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="14">
         <v>60</v>
@@ -5004,7 +5108,7 @@
     </row>
     <row r="35" spans="1:4" ht="25" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>38</v>
@@ -5018,10 +5122,10 @@
     </row>
     <row r="36" spans="1:4" ht="25" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="14">
         <v>20</v>
@@ -5032,10 +5136,10 @@
     </row>
     <row r="37" spans="1:4" ht="25" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" s="14">
         <v>60</v>
@@ -5046,10 +5150,10 @@
     </row>
     <row r="38" spans="1:4" ht="25" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C38" s="14">
         <v>20</v>
@@ -5060,10 +5164,10 @@
     </row>
     <row r="39" spans="1:4" ht="25" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C39" s="14">
         <v>20</v>
@@ -5074,10 +5178,10 @@
     </row>
     <row r="40" spans="1:4" ht="25" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="14">
         <v>20</v>
@@ -5088,7 +5192,7 @@
     </row>
     <row r="41" spans="1:4" ht="25" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>46</v>
@@ -5102,10 +5206,10 @@
     </row>
     <row r="42" spans="1:4" ht="25" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" s="14">
         <v>20</v>
@@ -5116,10 +5220,10 @@
     </row>
     <row r="43" spans="1:4" ht="25" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C43" s="14">
         <v>70</v>
@@ -5130,10 +5234,10 @@
     </row>
     <row r="44" spans="1:4" ht="25" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="14">
         <v>20</v>
@@ -5144,7 +5248,7 @@
     </row>
     <row r="45" spans="1:4" ht="25" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>38</v>
@@ -5158,10 +5262,10 @@
     </row>
     <row r="46" spans="1:4" ht="25" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" s="14">
         <v>40</v>
@@ -5172,10 +5276,10 @@
     </row>
     <row r="47" spans="1:4" ht="25" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="14">
         <v>20</v>
@@ -5186,10 +5290,10 @@
     </row>
     <row r="48" spans="1:4" ht="25" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="14">
         <v>30</v>
@@ -5200,10 +5304,10 @@
     </row>
     <row r="49" spans="1:4" ht="25" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C49" s="14">
         <v>20</v>
@@ -5214,10 +5318,10 @@
     </row>
     <row r="50" spans="1:4" ht="25" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C50" s="14">
         <v>40</v>
@@ -5228,7 +5332,7 @@
     </row>
     <row r="51" spans="1:4" ht="25" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>38</v>
@@ -5242,10 +5346,10 @@
     </row>
     <row r="52" spans="1:4" ht="25" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="14">
         <v>20</v>
@@ -5256,10 +5360,10 @@
     </row>
     <row r="53" spans="1:4" ht="25" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="14">
         <v>20</v>
@@ -5270,10 +5374,10 @@
     </row>
     <row r="54" spans="1:4" ht="25" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" s="14">
         <v>20</v>
@@ -5284,7 +5388,7 @@
     </row>
     <row r="55" spans="1:4" ht="25" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>46</v>
@@ -5298,10 +5402,10 @@
     </row>
     <row r="56" spans="1:4" ht="25" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="14">
         <v>20</v>
@@ -5312,10 +5416,10 @@
     </row>
     <row r="57" spans="1:4" ht="25" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="14">
         <v>55</v>
@@ -5326,10 +5430,10 @@
     </row>
     <row r="58" spans="1:4" ht="25" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C58" s="14">
         <v>20</v>
@@ -5340,10 +5444,10 @@
     </row>
     <row r="59" spans="1:4" ht="25" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="14">
         <v>20</v>
@@ -5354,7 +5458,7 @@
     </row>
     <row r="60" spans="1:4" ht="25" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>38</v>
@@ -5368,10 +5472,10 @@
     </row>
     <row r="61" spans="1:4" ht="25" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61" s="14">
         <v>20</v>
@@ -5382,10 +5486,10 @@
     </row>
     <row r="62" spans="1:4" ht="25" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="14">
         <v>40</v>
@@ -5396,10 +5500,10 @@
     </row>
     <row r="63" spans="1:4" ht="25" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C63" s="14">
         <v>20</v>
@@ -5410,10 +5514,10 @@
     </row>
     <row r="64" spans="1:4" ht="25" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" s="14">
         <v>20</v>
@@ -5424,7 +5528,7 @@
     </row>
     <row r="65" spans="1:4" ht="25" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>46</v>
@@ -5438,10 +5542,10 @@
     </row>
     <row r="66" spans="1:4" ht="25" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C66" s="14">
         <v>30</v>
@@ -5452,10 +5556,10 @@
     </row>
     <row r="67" spans="1:4" ht="25" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C67" s="14">
         <v>40</v>
@@ -5466,10 +5570,10 @@
     </row>
     <row r="68" spans="1:4" ht="25" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C68" s="14">
         <v>20</v>
@@ -5480,10 +5584,10 @@
     </row>
     <row r="69" spans="1:4" ht="25" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69" s="14">
         <v>20</v>
@@ -5494,10 +5598,10 @@
     </row>
     <row r="70" spans="1:4" ht="25" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C70" s="14">
         <v>20</v>
@@ -5508,10 +5612,10 @@
     </row>
     <row r="71" spans="1:4" ht="25" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="14">
         <v>20</v>
@@ -5522,10 +5626,10 @@
     </row>
     <row r="72" spans="1:4" ht="25" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C72" s="14">
         <v>40</v>
@@ -5536,10 +5640,10 @@
     </row>
     <row r="73" spans="1:4" ht="25" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C73" s="14">
         <v>20</v>
@@ -5550,10 +5654,10 @@
     </row>
     <row r="74" spans="1:4" ht="25" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C74" s="14">
         <v>40</v>
@@ -5564,7 +5668,7 @@
     </row>
     <row r="75" spans="1:4" ht="25" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>46</v>
@@ -5578,10 +5682,10 @@
     </row>
     <row r="76" spans="1:4" ht="25" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C76" s="14">
         <v>30</v>
@@ -5592,10 +5696,10 @@
     </row>
     <row r="77" spans="1:4" ht="25" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C77" s="14">
         <v>20</v>
@@ -5606,10 +5710,10 @@
     </row>
     <row r="78" spans="1:4" ht="25" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C78" s="14">
         <v>20</v>
@@ -5620,10 +5724,10 @@
     </row>
     <row r="79" spans="1:4" ht="25" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C79" s="14">
         <v>40</v>
@@ -5634,7 +5738,7 @@
     </row>
     <row r="80" spans="1:4" ht="25" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>38</v>
@@ -5648,10 +5752,10 @@
     </row>
     <row r="81" spans="1:4" ht="25" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C81" s="14">
         <v>20</v>
@@ -5662,10 +5766,10 @@
     </row>
     <row r="82" spans="1:4" ht="25" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C82" s="14">
         <v>20</v>
@@ -5676,10 +5780,10 @@
     </row>
     <row r="83" spans="1:4" ht="25" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C83" s="14">
         <v>20</v>
@@ -5690,10 +5794,10 @@
     </row>
     <row r="84" spans="1:4" ht="25" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C84" s="14">
         <v>100</v>
@@ -5704,10 +5808,10 @@
     </row>
     <row r="85" spans="1:4" ht="25" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C85" s="14">
         <v>40</v>
@@ -5718,7 +5822,7 @@
     </row>
     <row r="86" spans="1:4" ht="25" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>38</v>
@@ -5732,10 +5836,10 @@
     </row>
     <row r="87" spans="1:4" ht="25" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C87" s="14">
         <v>20</v>
@@ -5746,10 +5850,10 @@
     </row>
     <row r="88" spans="1:4" ht="25" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C88" s="14">
         <v>20</v>
@@ -5760,10 +5864,10 @@
     </row>
     <row r="89" spans="1:4" ht="25" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C89" s="14">
         <v>40</v>
@@ -5774,10 +5878,10 @@
     </row>
     <row r="90" spans="1:4" ht="25" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C90" s="14">
         <v>40</v>
@@ -5788,10 +5892,10 @@
     </row>
     <row r="91" spans="1:4" ht="25" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C91" s="14">
         <v>40</v>
@@ -5802,10 +5906,10 @@
     </row>
     <row r="92" spans="1:4" ht="25" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C92" s="14">
         <v>40</v>
@@ -5816,7 +5920,7 @@
     </row>
     <row r="93" spans="1:4" ht="25" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>38</v>
@@ -5830,10 +5934,10 @@
     </row>
     <row r="94" spans="1:4" ht="25" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C94" s="14">
         <v>20</v>
@@ -5844,7 +5948,7 @@
     </row>
     <row r="95" spans="1:4" ht="25" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>46</v>
@@ -5858,10 +5962,10 @@
     </row>
     <row r="96" spans="1:4" ht="25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C96" s="14">
         <v>40</v>
@@ -5872,10 +5976,10 @@
     </row>
     <row r="97" spans="1:4" ht="25" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C97" s="14">
         <v>20</v>
@@ -5886,10 +5990,10 @@
     </row>
     <row r="98" spans="1:4" ht="25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C98" s="14">
         <v>40</v>
@@ -5900,7 +6004,7 @@
     </row>
     <row r="99" spans="1:4" ht="25" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>46</v>
@@ -5914,10 +6018,10 @@
     </row>
     <row r="100" spans="1:4" ht="25" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C100" s="14">
         <v>80</v>
@@ -5928,10 +6032,10 @@
     </row>
     <row r="101" spans="1:4" ht="25" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C101" s="14">
         <v>25</v>
@@ -5942,7 +6046,7 @@
     </row>
     <row r="102" spans="1:4" ht="25" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>38</v>
@@ -5956,10 +6060,10 @@
     </row>
     <row r="103" spans="1:4" ht="25" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C103" s="14">
         <v>40</v>
@@ -5970,10 +6074,10 @@
     </row>
     <row r="104" spans="1:4" ht="25" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C104" s="14">
         <v>60</v>
@@ -5984,10 +6088,10 @@
     </row>
     <row r="105" spans="1:4" ht="25" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C105" s="14">
         <v>20</v>
@@ -5998,10 +6102,10 @@
     </row>
     <row r="106" spans="1:4" ht="25" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C106" s="14">
         <v>20</v>
@@ -6012,10 +6116,10 @@
     </row>
     <row r="107" spans="1:4" ht="25" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C107" s="14">
         <v>40</v>
@@ -6026,7 +6130,7 @@
     </row>
     <row r="108" spans="1:4" ht="25" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>46</v>
@@ -6040,10 +6144,10 @@
     </row>
     <row r="109" spans="1:4" ht="25" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C109" s="14">
         <v>20</v>
@@ -6054,10 +6158,10 @@
     </row>
     <row r="110" spans="1:4" ht="25" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C110" s="14">
         <v>20</v>
@@ -6068,10 +6172,10 @@
     </row>
     <row r="111" spans="1:4" ht="25" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C111" s="14">
         <v>20</v>
@@ -6082,10 +6186,10 @@
     </row>
     <row r="112" spans="1:4" ht="25" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C112" s="14">
         <v>20</v>
@@ -6096,10 +6200,10 @@
     </row>
     <row r="113" spans="1:4" ht="25" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C113" s="14">
         <v>20</v>
@@ -6110,10 +6214,10 @@
     </row>
     <row r="114" spans="1:4" ht="25" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C114" s="14">
         <v>50</v>
@@ -6124,10 +6228,10 @@
     </row>
     <row r="115" spans="1:4" ht="25" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C115" s="14">
         <v>20</v>
@@ -6138,7 +6242,7 @@
     </row>
     <row r="116" spans="1:4" ht="25" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>38</v>
@@ -6152,10 +6256,10 @@
     </row>
     <row r="117" spans="1:4" ht="25" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C117" s="14">
         <v>20</v>
@@ -6166,7 +6270,7 @@
     </row>
     <row r="118" spans="1:4" ht="25" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>46</v>
@@ -6180,10 +6284,10 @@
     </row>
     <row r="119" spans="1:4" ht="25" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C119" s="14">
         <v>20</v>
@@ -6194,10 +6298,10 @@
     </row>
     <row r="120" spans="1:4" ht="25" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C120" s="14">
         <v>40</v>
@@ -6208,10 +6312,10 @@
     </row>
     <row r="121" spans="1:4" ht="25" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C121" s="14">
         <v>70</v>
@@ -6222,10 +6326,10 @@
     </row>
     <row r="122" spans="1:4" ht="25" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C122" s="14">
         <v>60</v>
@@ -6236,10 +6340,10 @@
     </row>
     <row r="123" spans="1:4" ht="25" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C123" s="14">
         <v>40</v>
@@ -6250,10 +6354,10 @@
     </row>
     <row r="124" spans="1:4" ht="25" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C124" s="14">
         <v>20</v>
@@ -6264,10 +6368,10 @@
     </row>
     <row r="125" spans="1:4" ht="25" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C125" s="14">
         <v>40</v>
@@ -6278,10 +6382,10 @@
     </row>
     <row r="126" spans="1:4" ht="25" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C126" s="14">
         <v>40</v>
@@ -6292,10 +6396,10 @@
     </row>
     <row r="127" spans="1:4" ht="25" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C127" s="14">
         <v>40</v>
@@ -6306,10 +6410,10 @@
     </row>
     <row r="128" spans="1:4" ht="25" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C128" s="14">
         <v>20</v>
@@ -6320,10 +6424,10 @@
     </row>
     <row r="129" spans="1:4" ht="25" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C129" s="14">
         <v>20</v>
@@ -6334,10 +6438,10 @@
     </row>
     <row r="130" spans="1:4" ht="25" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C130" s="14">
         <v>20</v>
@@ -6348,7 +6452,7 @@
     </row>
     <row r="131" spans="1:4" ht="25" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>38</v>
@@ -6362,10 +6466,10 @@
     </row>
     <row r="132" spans="1:4" ht="25" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C132" s="14">
         <v>20</v>
@@ -6376,10 +6480,10 @@
     </row>
     <row r="133" spans="1:4" ht="25" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C133" s="14">
         <v>20</v>
@@ -6390,10 +6494,10 @@
     </row>
     <row r="134" spans="1:4" ht="25" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C134" s="14">
         <v>20</v>
@@ -6404,10 +6508,10 @@
     </row>
     <row r="135" spans="1:4" ht="25" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C135" s="14">
         <v>20</v>
@@ -6418,7 +6522,7 @@
     </row>
     <row r="136" spans="1:4" ht="25" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>38</v>
@@ -6432,10 +6536,10 @@
     </row>
     <row r="137" spans="1:4" ht="25" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C137" s="14">
         <v>20</v>
@@ -6446,10 +6550,10 @@
     </row>
     <row r="138" spans="1:4" ht="25" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C138" s="14">
         <v>20</v>
@@ -6460,10 +6564,10 @@
     </row>
     <row r="139" spans="1:4" ht="25" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C139" s="14">
         <v>40</v>
@@ -6474,10 +6578,10 @@
     </row>
     <row r="140" spans="1:4" ht="25" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C140" s="14">
         <v>80</v>
@@ -6488,10 +6592,10 @@
     </row>
     <row r="141" spans="1:4" ht="25" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C141" s="14">
         <v>40</v>
@@ -6502,7 +6606,7 @@
     </row>
     <row r="142" spans="1:4" ht="25" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>46</v>
@@ -6516,10 +6620,10 @@
     </row>
     <row r="143" spans="1:4" ht="25" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C143" s="14">
         <v>20</v>
@@ -6530,7 +6634,7 @@
     </row>
     <row r="144" spans="1:4" ht="25" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>46</v>
@@ -6544,10 +6648,10 @@
     </row>
     <row r="145" spans="1:4" ht="25" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C145" s="14">
         <v>20</v>
@@ -6558,10 +6662,10 @@
     </row>
     <row r="146" spans="1:4" ht="25" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C146" s="14">
         <v>40</v>
@@ -6572,10 +6676,10 @@
     </row>
     <row r="147" spans="1:4" ht="25" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C147" s="14">
         <v>50</v>
@@ -6586,7 +6690,7 @@
     </row>
     <row r="148" spans="1:4" ht="25" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>38</v>
@@ -6600,10 +6704,10 @@
     </row>
     <row r="149" spans="1:4" ht="25" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C149" s="14">
         <v>20</v>
@@ -6614,10 +6718,10 @@
     </row>
     <row r="150" spans="1:4" ht="25" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C150" s="14">
         <v>20</v>
@@ -6628,10 +6732,10 @@
     </row>
     <row r="151" spans="1:4" ht="25" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C151" s="14">
         <v>40</v>
@@ -6642,10 +6746,10 @@
     </row>
     <row r="152" spans="1:4" ht="25" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C152" s="14">
         <v>20</v>
@@ -6656,10 +6760,10 @@
     </row>
     <row r="153" spans="1:4" ht="25" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C153" s="14">
         <v>20</v>
@@ -6670,10 +6774,10 @@
     </row>
     <row r="154" spans="1:4" ht="25" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C154" s="14">
         <v>20</v>
@@ -6684,10 +6788,10 @@
     </row>
     <row r="155" spans="1:4" ht="25" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C155" s="14">
         <v>40</v>
@@ -6698,10 +6802,10 @@
     </row>
     <row r="156" spans="1:4" ht="25" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C156" s="14">
         <v>20</v>
@@ -6712,10 +6816,10 @@
     </row>
     <row r="157" spans="1:4" ht="25" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C157" s="14">
         <v>40</v>
@@ -6726,10 +6830,10 @@
     </row>
     <row r="158" spans="1:4" ht="25" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C158" s="14">
         <v>20</v>
@@ -6740,10 +6844,10 @@
     </row>
     <row r="159" spans="1:4" ht="25" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C159" s="14">
         <v>40</v>
@@ -6754,10 +6858,10 @@
     </row>
     <row r="160" spans="1:4" ht="25" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C160" s="14">
         <v>20</v>
@@ -6768,7 +6872,7 @@
     </row>
     <row r="161" spans="1:4" ht="25" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>38</v>
@@ -6782,10 +6886,10 @@
     </row>
     <row r="162" spans="1:4" ht="25" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C162" s="14">
         <v>20</v>
@@ -6796,7 +6900,7 @@
     </row>
     <row r="163" spans="1:4" ht="25" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>46</v>
@@ -6810,10 +6914,10 @@
     </row>
     <row r="164" spans="1:4" ht="25" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C164" s="14">
         <v>20</v>
@@ -6824,10 +6928,10 @@
     </row>
     <row r="165" spans="1:4" ht="25" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C165" s="14">
         <v>80</v>
@@ -6838,10 +6942,10 @@
     </row>
     <row r="166" spans="1:4" ht="25" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C166" s="14">
         <v>60</v>
@@ -6852,10 +6956,10 @@
     </row>
     <row r="167" spans="1:4" ht="25" customHeight="1">
       <c r="A167" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C167" s="14">
         <v>40</v>
@@ -6866,7 +6970,7 @@
     </row>
     <row r="168" spans="1:4" ht="25" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>38</v>
@@ -6880,10 +6984,10 @@
     </row>
     <row r="169" spans="1:4" ht="25" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C169" s="14">
         <v>20</v>
@@ -6894,10 +6998,10 @@
     </row>
     <row r="170" spans="1:4" ht="25" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C170" s="14">
         <v>60</v>
@@ -6908,10 +7012,10 @@
     </row>
     <row r="171" spans="1:4" ht="25" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C171" s="14">
         <v>40</v>
@@ -6922,24 +7026,24 @@
     </row>
     <row r="172" spans="1:4" ht="25" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C172" s="14">
         <v>20</v>
       </c>
       <c r="D172" s="14">
-        <v>39.1</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="25" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C173" s="14">
         <v>40</v>
@@ -6950,24 +7054,24 @@
     </row>
     <row r="174" spans="1:4" ht="25" customHeight="1">
       <c r="A174" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C174" s="14">
         <v>20</v>
       </c>
       <c r="D174" s="14">
-        <v>36.700000000000003</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="25" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C175" s="14">
         <v>40</v>
@@ -6978,10 +7082,10 @@
     </row>
     <row r="176" spans="1:4" ht="25" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C176" s="14">
         <v>20</v>
@@ -6992,21 +7096,21 @@
     </row>
     <row r="177" spans="1:4" ht="25" customHeight="1">
       <c r="A177" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C177" s="14">
         <v>20</v>
       </c>
       <c r="D177" s="14">
-        <v>21.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="25" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>38</v>
@@ -7015,7 +7119,7 @@
         <v>40</v>
       </c>
       <c r="D178" s="14">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
     </row>
   </sheetData>
@@ -7054,71 +7158,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="77" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1">
+      <c r="A2" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B2" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C2" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D2" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E2" s="78" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
+    <row r="3" spans="1:5" ht="24" customHeight="1">
+      <c r="A3" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B3" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C3" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D3" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E3" s="79" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="81" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17">
       <c r="A4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="D4" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="E4" s="36" t="s">
         <v>123</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30">
@@ -7126,16 +7230,16 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="D5" t="s">
         <v>126</v>
       </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
       <c r="E5" s="38">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16">
@@ -7143,16 +7247,16 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
         <v>128</v>
       </c>
-      <c r="C6" t="s">
-        <v>129</v>
-      </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16">
@@ -7160,27 +7264,33 @@
         <v>42</v>
       </c>
       <c r="B7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" t="s">
         <v>130</v>
       </c>
-      <c r="C7" t="s">
-        <v>131</v>
-      </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16">
+      <c r="A8" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8">
         <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16">
-      <c r="A8" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -7221,77 +7331,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="79" t="s">
-        <v>134</v>
+      <c r="A1" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="77" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="G2" s="80" t="s">
-        <v>135</v>
+      <c r="A2" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="78" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="G3" s="81" t="s">
-        <v>136</v>
+      <c r="A3" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="79" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17">
       <c r="A4" s="36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>30</v>
@@ -7300,72 +7410,72 @@
         <v>29</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="51">
       <c r="A5" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="58">
+        <v>138</v>
+      </c>
+      <c r="B5" s="55">
         <v>46243</v>
       </c>
-      <c r="C5" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>142</v>
+      <c r="C5" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>139</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="55">
         <v>46305</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B6" s="59">
+        <v>140</v>
+      </c>
+      <c r="B6" s="56">
         <v>46236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="54" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="59">
+        <v>143</v>
+      </c>
+      <c r="B7" s="56">
         <v>46236</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="54" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7389,7 +7499,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7399,63 +7509,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+    </row>
+    <row r="2" spans="1:5" ht="28" customHeight="1">
+      <c r="A2" s="84" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+    </row>
+    <row r="3" spans="1:5" ht="28" customHeight="1">
+      <c r="A3" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-    </row>
-    <row r="2" spans="1:5" ht="28" customHeight="1">
-      <c r="A2" s="86" t="s">
+      <c r="C4" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-    </row>
-    <row r="3" spans="1:5" ht="28" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="D4" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="66" t="s">
+      <c r="E4" s="63" t="s">
         <v>150</v>
-      </c>
-      <c r="C4" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="66" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16">
       <c r="A5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="66">
+      <c r="B5" s="63">
         <v>1</v>
       </c>
-      <c r="C5" s="66">
-        <v>20</v>
-      </c>
-      <c r="D5" s="67">
+      <c r="C5" s="63">
+        <v>20</v>
+      </c>
+      <c r="D5" s="64">
         <v>0.1</v>
       </c>
-      <c r="E5" s="67">
+      <c r="E5" s="64">
         <v>0.2</v>
       </c>
     </row>
@@ -7498,7 +7608,7 @@
         <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -7543,7 +7653,7 @@
         <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C11">
         <v>15</v>
@@ -7656,7 +7766,7 @@
         <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -7721,7 +7831,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>0.25</v>
@@ -7738,7 +7848,7 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>0.5</v>
@@ -7755,7 +7865,7 @@
         <v>3</v>
       </c>
       <c r="C24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>0.75</v>
@@ -7769,7 +7879,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -7803,10 +7913,10 @@
         <v>20</v>
       </c>
       <c r="D27">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E27">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16">
@@ -7820,10 +7930,10 @@
         <v>20</v>
       </c>
       <c r="D28">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16">
@@ -7831,7 +7941,7 @@
         <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -7848,10 +7958,10 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16">
@@ -7865,10 +7975,10 @@
         <v>15</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16">
@@ -7882,10 +7992,10 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16">
@@ -7899,10 +8009,10 @@
         <v>15</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16">
@@ -7910,7 +8020,7 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -7927,10 +8037,10 @@
         <v>15</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16">
@@ -7944,10 +8054,10 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16">
@@ -7961,26 +8071,9 @@
         <v>15</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E37">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="16">
-      <c r="A38" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38">
-        <v>14</v>
-      </c>
-      <c r="C38">
-        <v>15</v>
-      </c>
-      <c r="D38">
-        <v>12</v>
-      </c>
-      <c r="E38">
         <v>25</v>
       </c>
     </row>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95623EA-0F29-2546-AB55-FC3E4A7B9CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9376D0-85A1-D24D-B4F9-F3560AEFF3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -561,10 +561,10 @@
     <t>Saturday 10/3/26</t>
   </si>
   <si>
-    <t>/photos/october2026tourney.heic</t>
-  </si>
-  <si>
     <t>October 2026 tournament winner: Adam B.</t>
+  </si>
+  <si>
+    <t>/photos/october2026tourney.HEIC</t>
   </si>
 </sst>
 </file>
@@ -7281,10 +7281,10 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" t="s">
         <v>173</v>
-      </c>
-      <c r="C8" t="s">
-        <v>174</v>
       </c>
       <c r="D8" t="s">
         <v>126</v>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9376D0-85A1-D24D-B4F9-F3560AEFF3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA5A806-16BF-6D4B-A651-E5EF639B08DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="177">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -565,6 +565,12 @@
   </si>
   <si>
     <t>/photos/october2026tourney.HEIC</t>
+  </si>
+  <si>
+    <t>cash-game-2026-10-07</t>
+  </si>
+  <si>
+    <t>Wednesday 10/7/26</t>
   </si>
 </sst>
 </file>
@@ -1108,60 +1114,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="18" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="12" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1173,6 +1125,60 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,15 +1225,6 @@
           <bgColor rgb="FFE5E7EB"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1327,19 +1324,68 @@
       <font>
         <u val="none"/>
         <sz val="12"/>
-        <color rgb="FF17231D"/>
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border>
-        <left/>
-        <right style="thin">
-          <color rgb="FFE3EAE6"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1401,59 +1447,19 @@
       <font>
         <u val="none"/>
         <sz val="12"/>
+        <color rgb="FF17231D"/>
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color rgb="FFE3EAE6"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1486,24 +1492,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I56" totalsRowShown="0" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I56" totalsRowShown="0" dataDxfId="27">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I25" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I26" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1520,15 +1526,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D178" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D184" totalsRowShown="0" dataDxfId="17">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1538,7 +1544,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EventPhotosTable" displayName="EventPhotosTable" ref="A4:E8" totalsRowShown="0">
   <autoFilter ref="A4:E8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Image Path"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Caption"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Show on Home"/>
@@ -1549,16 +1555,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="AnnouncementsTable" displayName="AnnouncementsTable" ref="A4:G7" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A4:G7" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Date" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Title" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Body" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Announcement ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Date" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Title" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Body" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Event ID" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Expires" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pinned" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1567,7 +1573,7 @@
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="BlindSchedulesTable" displayName="BlindSchedulesTable" ref="A4:E37" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Tournament ID" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Level"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Duration"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Small Blind"/>
@@ -1889,22 +1895,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="78" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1916,22 +1922,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="80" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1943,49 +1949,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="78" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="80" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -1997,22 +2003,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="78" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -2024,237 +2030,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="80" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A509)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73" t="s">
+      <c r="E14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="H14" s="81" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="70" t="s">
+      <c r="E15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="70" t="s">
+      <c r="G15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="77" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="79" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="70" t="s">
+      <c r="A17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="77" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="69" t="s">
+      <c r="D18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="69" t="s">
+      <c r="E18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="79" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="70" t="s">
+      <c r="E19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="70" t="s">
+      <c r="G19" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="70" t="s">
+      <c r="H19" s="77" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="79" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2279,89 +2285,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="77" t="s">
+      <c r="H1" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="77" t="s">
+      <c r="I1" s="71" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="D2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="78" t="s">
+      <c r="G2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="78" t="s">
+      <c r="H2" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="72" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="73" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2541,43 +2547,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -2627,7 +2633,7 @@
       <c r="F5" s="44">
         <v>0</v>
       </c>
-      <c r="G5" s="87"/>
+      <c r="G5" s="67"/>
       <c r="H5" s="47"/>
       <c r="I5" s="48"/>
     </row>
@@ -2650,7 +2656,7 @@
       <c r="F6" s="45">
         <v>0</v>
       </c>
-      <c r="G6" s="88"/>
+      <c r="G6" s="68"/>
       <c r="H6" s="49"/>
       <c r="I6" s="50"/>
     </row>
@@ -2673,7 +2679,7 @@
       <c r="F7" s="46">
         <v>0</v>
       </c>
-      <c r="G7" s="89"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="51"/>
       <c r="I7" s="52"/>
     </row>
@@ -2696,7 +2702,7 @@
       <c r="F8" s="45">
         <v>0</v>
       </c>
-      <c r="G8" s="88"/>
+      <c r="G8" s="68"/>
       <c r="H8" s="49"/>
       <c r="I8" s="50"/>
     </row>
@@ -2719,7 +2725,7 @@
       <c r="F9" s="46">
         <v>0</v>
       </c>
-      <c r="G9" s="89"/>
+      <c r="G9" s="69"/>
       <c r="H9" s="51"/>
       <c r="I9" s="52"/>
     </row>
@@ -2742,7 +2748,7 @@
       <c r="F10" s="45">
         <v>0</v>
       </c>
-      <c r="G10" s="88"/>
+      <c r="G10" s="68"/>
       <c r="H10" s="49"/>
       <c r="I10" s="50"/>
     </row>
@@ -2765,7 +2771,7 @@
       <c r="F11" s="46">
         <v>0</v>
       </c>
-      <c r="G11" s="89"/>
+      <c r="G11" s="69"/>
       <c r="H11" s="51"/>
       <c r="I11" s="52"/>
     </row>
@@ -2788,7 +2794,7 @@
       <c r="F12" s="45">
         <v>0</v>
       </c>
-      <c r="G12" s="88"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="49"/>
       <c r="I12" s="50"/>
     </row>
@@ -2811,7 +2817,7 @@
       <c r="F13" s="46">
         <v>0</v>
       </c>
-      <c r="G13" s="89"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="51"/>
       <c r="I13" s="52"/>
     </row>
@@ -2834,7 +2840,7 @@
       <c r="F14" s="45">
         <v>0</v>
       </c>
-      <c r="G14" s="88"/>
+      <c r="G14" s="68"/>
       <c r="H14" s="49"/>
       <c r="I14" s="50"/>
     </row>
@@ -2857,7 +2863,7 @@
       <c r="F15" s="46">
         <v>0</v>
       </c>
-      <c r="G15" s="89"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="51"/>
       <c r="I15" s="52"/>
     </row>
@@ -2880,7 +2886,7 @@
       <c r="F16" s="46">
         <v>0</v>
       </c>
-      <c r="G16" s="89"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="51"/>
       <c r="I16" s="52"/>
     </row>
@@ -2903,7 +2909,7 @@
       <c r="F17" s="45">
         <v>0</v>
       </c>
-      <c r="G17" s="88"/>
+      <c r="G17" s="68"/>
       <c r="H17" s="49"/>
       <c r="I17" s="50"/>
     </row>
@@ -2926,7 +2932,7 @@
       <c r="F18" s="46">
         <v>0</v>
       </c>
-      <c r="G18" s="89"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="51"/>
       <c r="I18" s="52"/>
     </row>
@@ -2949,7 +2955,7 @@
       <c r="F19" s="45">
         <v>0</v>
       </c>
-      <c r="G19" s="88"/>
+      <c r="G19" s="68"/>
       <c r="H19" s="49"/>
       <c r="I19" s="50"/>
     </row>
@@ -2972,7 +2978,7 @@
       <c r="F20" s="46">
         <v>0</v>
       </c>
-      <c r="G20" s="89"/>
+      <c r="G20" s="69"/>
       <c r="H20" s="51"/>
       <c r="I20" s="52"/>
     </row>
@@ -2995,7 +3001,7 @@
       <c r="F21" s="45">
         <v>0</v>
       </c>
-      <c r="G21" s="88"/>
+      <c r="G21" s="68"/>
       <c r="H21" s="49"/>
       <c r="I21" s="50"/>
     </row>
@@ -3018,7 +3024,7 @@
       <c r="F22" s="46">
         <v>0</v>
       </c>
-      <c r="G22" s="89"/>
+      <c r="G22" s="69"/>
       <c r="H22" s="51"/>
       <c r="I22" s="52"/>
     </row>
@@ -3041,7 +3047,7 @@
       <c r="F23" s="45">
         <v>0</v>
       </c>
-      <c r="G23" s="88"/>
+      <c r="G23" s="68"/>
       <c r="H23" s="49"/>
       <c r="I23" s="50"/>
     </row>
@@ -3064,7 +3070,7 @@
       <c r="F24" s="46">
         <v>0</v>
       </c>
-      <c r="G24" s="89"/>
+      <c r="G24" s="69"/>
       <c r="H24" s="51"/>
       <c r="I24" s="52"/>
     </row>
@@ -3087,7 +3093,7 @@
       <c r="F25" s="45">
         <v>0</v>
       </c>
-      <c r="G25" s="88"/>
+      <c r="G25" s="68"/>
       <c r="H25" s="49"/>
       <c r="I25" s="50"/>
     </row>
@@ -3110,7 +3116,7 @@
       <c r="F26" s="46">
         <v>0</v>
       </c>
-      <c r="G26" s="89"/>
+      <c r="G26" s="69"/>
       <c r="H26" s="51"/>
       <c r="I26" s="52"/>
     </row>
@@ -3133,7 +3139,7 @@
       <c r="F27" s="45">
         <v>0</v>
       </c>
-      <c r="G27" s="88"/>
+      <c r="G27" s="68"/>
       <c r="H27" s="49"/>
       <c r="I27" s="50"/>
     </row>
@@ -3156,7 +3162,7 @@
       <c r="F28" s="46">
         <v>0</v>
       </c>
-      <c r="G28" s="89"/>
+      <c r="G28" s="69"/>
       <c r="H28" s="51"/>
       <c r="I28" s="52"/>
     </row>
@@ -3179,7 +3185,7 @@
       <c r="F29" s="45">
         <v>0</v>
       </c>
-      <c r="G29" s="88"/>
+      <c r="G29" s="68"/>
       <c r="H29" s="49"/>
       <c r="I29" s="50"/>
     </row>
@@ -3202,7 +3208,7 @@
       <c r="F30" s="46">
         <v>0</v>
       </c>
-      <c r="G30" s="89"/>
+      <c r="G30" s="69"/>
       <c r="H30" s="51"/>
       <c r="I30" s="52"/>
     </row>
@@ -3225,7 +3231,7 @@
       <c r="F31" s="45">
         <v>0</v>
       </c>
-      <c r="G31" s="88"/>
+      <c r="G31" s="68"/>
       <c r="H31" s="49"/>
       <c r="I31" s="50"/>
     </row>
@@ -3248,7 +3254,7 @@
       <c r="F32" s="46">
         <v>0</v>
       </c>
-      <c r="G32" s="89"/>
+      <c r="G32" s="69"/>
       <c r="H32" s="51"/>
       <c r="I32" s="52"/>
     </row>
@@ -3271,7 +3277,7 @@
       <c r="F33" s="45">
         <v>0</v>
       </c>
-      <c r="G33" s="88"/>
+      <c r="G33" s="68"/>
       <c r="H33" s="49"/>
       <c r="I33" s="50"/>
     </row>
@@ -3294,7 +3300,7 @@
       <c r="F34" s="46">
         <v>0</v>
       </c>
-      <c r="G34" s="89"/>
+      <c r="G34" s="69"/>
       <c r="H34" s="51"/>
       <c r="I34" s="52"/>
     </row>
@@ -3317,7 +3323,7 @@
       <c r="F35" s="45">
         <v>0</v>
       </c>
-      <c r="G35" s="88">
+      <c r="G35" s="68">
         <v>4</v>
       </c>
       <c r="H35" s="49">
@@ -3346,7 +3352,7 @@
       <c r="F36" s="46">
         <v>0</v>
       </c>
-      <c r="G36" s="89">
+      <c r="G36" s="69">
         <v>5</v>
       </c>
       <c r="H36" s="51">
@@ -3375,7 +3381,7 @@
       <c r="F37" s="45">
         <v>0</v>
       </c>
-      <c r="G37" s="88">
+      <c r="G37" s="68">
         <v>5</v>
       </c>
       <c r="H37" s="49">
@@ -3404,7 +3410,7 @@
       <c r="F38" s="46">
         <v>0</v>
       </c>
-      <c r="G38" s="89">
+      <c r="G38" s="69">
         <v>6</v>
       </c>
       <c r="H38" s="51">
@@ -3433,7 +3439,7 @@
       <c r="F39" s="45">
         <v>0</v>
       </c>
-      <c r="G39" s="88">
+      <c r="G39" s="68">
         <v>6</v>
       </c>
       <c r="H39" s="49">
@@ -3462,7 +3468,7 @@
       <c r="F40" s="46">
         <v>0</v>
       </c>
-      <c r="G40" s="89">
+      <c r="G40" s="69">
         <v>6</v>
       </c>
       <c r="H40" s="51">
@@ -3491,7 +3497,7 @@
       <c r="F41" s="45">
         <v>0</v>
       </c>
-      <c r="G41" s="88">
+      <c r="G41" s="68">
         <v>6</v>
       </c>
       <c r="H41" s="49">
@@ -3520,7 +3526,7 @@
       <c r="F42" s="46">
         <v>0</v>
       </c>
-      <c r="G42" s="89">
+      <c r="G42" s="69">
         <v>7</v>
       </c>
       <c r="H42" s="51">
@@ -3549,7 +3555,7 @@
       <c r="F43" s="45">
         <v>0</v>
       </c>
-      <c r="G43" s="88">
+      <c r="G43" s="68">
         <v>9</v>
       </c>
       <c r="H43" s="49">
@@ -3578,7 +3584,7 @@
       <c r="F44" s="46">
         <v>0</v>
       </c>
-      <c r="G44" s="89">
+      <c r="G44" s="69">
         <v>10</v>
       </c>
       <c r="H44" s="51">
@@ -3607,7 +3613,7 @@
       <c r="F45" s="45">
         <v>0</v>
       </c>
-      <c r="G45" s="88">
+      <c r="G45" s="68">
         <v>11</v>
       </c>
       <c r="H45" s="49">
@@ -3636,7 +3642,7 @@
       <c r="F46" s="46">
         <v>0</v>
       </c>
-      <c r="G46" s="89">
+      <c r="G46" s="69">
         <v>12</v>
       </c>
       <c r="H46" s="51">
@@ -3665,7 +3671,7 @@
       <c r="F47" s="45">
         <v>0</v>
       </c>
-      <c r="G47" s="88">
+      <c r="G47" s="68">
         <v>13</v>
       </c>
       <c r="H47" s="49">
@@ -3694,7 +3700,7 @@
       <c r="F48" s="46">
         <v>0</v>
       </c>
-      <c r="G48" s="89"/>
+      <c r="G48" s="69"/>
       <c r="H48" s="51"/>
       <c r="I48" s="52"/>
     </row>
@@ -3717,10 +3723,10 @@
       <c r="F49" s="14">
         <v>0</v>
       </c>
-      <c r="G49" s="90">
+      <c r="G49" s="70">
         <v>4</v>
       </c>
-      <c r="H49" s="86">
+      <c r="H49" s="66">
         <v>0.86875000000000002</v>
       </c>
     </row>
@@ -3743,10 +3749,10 @@
       <c r="F50" s="14">
         <v>0</v>
       </c>
-      <c r="G50" s="90">
+      <c r="G50" s="70">
         <v>5</v>
       </c>
-      <c r="H50" s="86">
+      <c r="H50" s="66">
         <v>0.88194444444444442</v>
       </c>
     </row>
@@ -3769,7 +3775,7 @@
       <c r="F51" s="14">
         <v>0</v>
       </c>
-      <c r="G51" s="90"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:8" ht="28" customHeight="1">
       <c r="A52" s="1" t="s">
@@ -3790,10 +3796,10 @@
       <c r="F52" s="14">
         <v>0</v>
       </c>
-      <c r="G52" s="90">
+      <c r="G52" s="70">
         <v>6</v>
       </c>
-      <c r="H52" s="86">
+      <c r="H52" s="66">
         <v>0.8930555555555556</v>
       </c>
     </row>
@@ -3816,10 +3822,10 @@
       <c r="F53" s="14">
         <v>0</v>
       </c>
-      <c r="G53" s="90">
+      <c r="G53" s="70">
         <v>11</v>
       </c>
-      <c r="H53" s="86">
+      <c r="H53" s="66">
         <v>0.96388888888888891</v>
       </c>
     </row>
@@ -3842,10 +3848,10 @@
       <c r="F54" s="14">
         <v>0</v>
       </c>
-      <c r="G54" s="90">
+      <c r="G54" s="70">
         <v>12</v>
       </c>
-      <c r="H54" s="86">
+      <c r="H54" s="66">
         <v>0.97847222222222219</v>
       </c>
     </row>
@@ -3868,10 +3874,10 @@
       <c r="F55" s="14">
         <v>0</v>
       </c>
-      <c r="G55" s="90">
+      <c r="G55" s="70">
         <v>5</v>
       </c>
-      <c r="H55" s="86">
+      <c r="H55" s="66">
         <v>0.87847222222222221</v>
       </c>
     </row>
@@ -3894,10 +3900,10 @@
       <c r="F56" s="14">
         <v>0</v>
       </c>
-      <c r="G56" s="90">
+      <c r="G56" s="70">
         <v>8</v>
       </c>
-      <c r="H56" s="86">
+      <c r="H56" s="66">
         <v>0.92986111111111114</v>
       </c>
     </row>
@@ -3926,7 +3932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3943,89 +3949,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="77" t="s">
+      <c r="H1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="77" t="s">
+      <c r="I1" s="71" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="19" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="D2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="78" t="s">
+      <c r="G2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="78" t="s">
+      <c r="H2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="72" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="73" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4605,6 +4611,32 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H25" s="65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="19" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="28">
+        <v>46302</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="62">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H26" s="65">
         <v>20</v>
       </c>
     </row>
@@ -4621,7 +4653,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F25 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F26 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4638,7 +4670,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -4649,28 +4681,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="84" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -7120,6 +7152,90 @@
       </c>
       <c r="D178" s="14">
         <v>54.4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="25" customHeight="1">
+      <c r="A179" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C179" s="14">
+        <v>30</v>
+      </c>
+      <c r="D179" s="14">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="25" customHeight="1">
+      <c r="A180" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C180" s="14">
+        <v>20</v>
+      </c>
+      <c r="D180" s="14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="25" customHeight="1">
+      <c r="A181" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C181" s="14">
+        <v>20</v>
+      </c>
+      <c r="D181" s="14">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="25" customHeight="1">
+      <c r="A182" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C182" s="14">
+        <v>30</v>
+      </c>
+      <c r="D182" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="25" customHeight="1">
+      <c r="A183" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C183" s="14">
+        <v>20</v>
+      </c>
+      <c r="D183" s="14">
+        <v>35.299999999999997</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="25" customHeight="1">
+      <c r="A184" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C184" s="14">
+        <v>20</v>
+      </c>
+      <c r="D184" s="14">
+        <v>19.899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7158,53 +7274,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="71" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="D2" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="72" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="73" t="s">
         <v>118</v>
       </c>
     </row>
@@ -7331,71 +7447,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="71" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="D2" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="78" t="s">
+      <c r="G2" s="72" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="73" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7509,31 +7625,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="63" t="s">

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA5A806-16BF-6D4B-A651-E5EF639B08DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190C636F-F331-4D40-A5A8-6000512A499E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="179">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>Wednesday 10/7/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-10-21</t>
+  </si>
+  <si>
+    <t>Wednesday 10/21/26</t>
   </si>
 </sst>
 </file>
@@ -1125,6 +1131,37 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1134,43 +1171,12 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1324,43 +1330,19 @@
       <font>
         <u val="none"/>
         <sz val="12"/>
+        <color rgb="FF17231D"/>
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color rgb="FFE3EAE6"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1447,19 +1429,43 @@
       <font>
         <u val="none"/>
         <sz val="12"/>
-        <color rgb="FF17231D"/>
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border>
-        <left/>
-        <right style="thin">
-          <color rgb="FFE3EAE6"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1492,24 +1498,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I56" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TournamentResultsTable" displayName="TournamentResultsTable" ref="A4:I56" totalsRowShown="0" dataDxfId="23">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tournament ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Total Buy-In" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Placement" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Placement Payout" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Bonus Payout" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Elimination Level" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Eliminated At" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Eliminated By" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I26" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I27" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1526,15 +1532,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D184" totalsRowShown="0" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D189" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cash Game ID" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Amount Buy-In" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Amount At End" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1544,7 +1550,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EventPhotosTable" displayName="EventPhotosTable" ref="A4:E8" totalsRowShown="0">
   <autoFilter ref="A4:E8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Event ID" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Image Path"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Caption"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Show on Home"/>
@@ -1788,106 +1794,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="74" t="s">
+      <c r="A1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="79" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="74" t="s">
+      <c r="A2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="79" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="75" t="s">
+      <c r="H3" s="80" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="81" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1895,22 +1901,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="77" t="s">
+      <c r="C6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="77" t="s">
+      <c r="E6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="78" t="s">
+      <c r="F6" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="76" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1922,22 +1928,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="80" t="s">
+      <c r="F7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="80" t="s">
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1949,49 +1955,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="77" t="s">
+      <c r="C8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="77" t="s">
+      <c r="D8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="76" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="79" t="s">
+      <c r="E9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="80" t="s">
+      <c r="F9" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="80" t="s">
+      <c r="G9" s="77" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -2003,22 +2009,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="77" t="s">
+      <c r="C10" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="77" t="s">
+      <c r="D10" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="76" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -2030,237 +2036,237 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="80" t="s">
+      <c r="F11" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="77" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A509)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="81" t="s">
+      <c r="D14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="81" t="s">
+      <c r="E14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="81" t="s">
+      <c r="F14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="81" t="s">
+      <c r="H14" s="78" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="77" t="s">
+      <c r="E15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="77" t="s">
+      <c r="F15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="77" t="s">
+      <c r="G15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="77" t="s">
+      <c r="H15" s="75" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="79" t="s">
+      <c r="D16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="79" t="s">
+      <c r="E16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="79" t="s">
+      <c r="F16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="79" t="s">
+      <c r="G16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="79" t="s">
+      <c r="H16" s="74" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="77" t="s">
+      <c r="A17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="75" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="79" t="s">
+      <c r="B18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="79" t="s">
+      <c r="D18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="79" t="s">
+      <c r="E18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="79" t="s">
+      <c r="F18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="79" t="s">
+      <c r="G18" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="79" t="s">
+      <c r="H18" s="74" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="77" t="s">
+      <c r="E19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="77" t="s">
+      <c r="G19" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="77" t="s">
+      <c r="H19" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="79" t="s">
+      <c r="B20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="79" t="s">
+      <c r="D20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="79" t="s">
+      <c r="E20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="79" t="s">
+      <c r="F20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="79" t="s">
+      <c r="G20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="79" t="s">
+      <c r="H20" s="74" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2285,89 +2291,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="71" t="s">
+      <c r="F1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="82" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="83" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="84" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2547,43 +2553,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -3932,7 +3938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3949,89 +3955,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="71" t="s">
+      <c r="F1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="82" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="19" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="83" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="84" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4637,6 +4643,32 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="H26" s="65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="19" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27" s="28">
+        <v>46316</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="62">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H27" s="65">
         <v>20</v>
       </c>
     </row>
@@ -4653,7 +4685,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F26 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F27 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4670,7 +4702,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D189"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -4681,28 +4713,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -7236,6 +7268,76 @@
       </c>
       <c r="D184" s="14">
         <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="25" customHeight="1">
+      <c r="A185" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C185" s="14">
+        <v>20</v>
+      </c>
+      <c r="D185" s="14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="25" customHeight="1">
+      <c r="A186" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C186" s="14">
+        <v>60</v>
+      </c>
+      <c r="D186" s="14">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="25" customHeight="1">
+      <c r="A187" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C187" s="14">
+        <v>20</v>
+      </c>
+      <c r="D187" s="14">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="25" customHeight="1">
+      <c r="A188" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C188" s="14">
+        <v>40</v>
+      </c>
+      <c r="D188" s="14">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="25" customHeight="1">
+      <c r="A189" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C189" s="14">
+        <v>20</v>
+      </c>
+      <c r="D189" s="14">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7274,53 +7376,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="82" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="83" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="84" t="s">
         <v>118</v>
       </c>
     </row>
@@ -7447,71 +7549,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="71" t="s">
+      <c r="F1" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="82" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="83" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="84" t="s">
         <v>133</v>
       </c>
     </row>

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190C636F-F331-4D40-A5A8-6000512A499E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F9B0FD-D043-2542-90CA-3B9D92EFE9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="181">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -577,14 +577,19 @@
   </si>
   <si>
     <t>Wednesday 10/21/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-10-24</t>
+  </si>
+  <si>
+    <t>Saturday 10/24/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
@@ -959,7 +964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1119,7 +1124,6 @@
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="12" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1515,7 +1519,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I27" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I28" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1532,7 +1536,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D189" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D199" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1794,106 +1798,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="79" t="s">
+      <c r="A1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="78" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1">
-      <c r="A2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="79" t="s">
+      <c r="A2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="78" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="80" t="s">
+      <c r="E3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="80" t="s">
+      <c r="G3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="80" t="s">
+      <c r="H3" s="79" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="81" t="s">
+      <c r="G5" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="80" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1901,22 +1905,22 @@
       <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="75" t="s">
+      <c r="E6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="76" t="s">
+      <c r="G6" s="75" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="40">
@@ -1928,22 +1932,22 @@
       <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="74" t="s">
+      <c r="E7" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="77" t="s">
+      <c r="G7" s="76" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="41">
@@ -1955,49 +1959,49 @@
       <c r="A8" s="39">
         <v>3</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="76" t="s">
+      <c r="G8" s="75" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="39">
         <v>4</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="76" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="41">
@@ -2009,22 +2013,22 @@
       <c r="A10" s="39">
         <v>5</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="75" t="s">
+      <c r="C10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="76" t="s">
+      <c r="G10" s="75" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="40">
@@ -2036,209 +2040,209 @@
       <c r="A11" s="39">
         <v>6</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="74" t="s">
+      <c r="E11" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="77" t="s">
+      <c r="G11" s="76" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A509)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
     <row r="14" spans="1:8" ht="28" customHeight="1">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="78" t="s">
+      <c r="F14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="78" t="s">
+      <c r="G14" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="77" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="75" t="s">
+      <c r="C15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="75" t="s">
+      <c r="G15" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="75" t="s">
+      <c r="H15" s="74" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="74" t="s">
+      <c r="E16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="74" t="s">
+      <c r="F16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="74" t="s">
+      <c r="G16" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="73" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="75" t="s">
+      <c r="A17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="74" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24" customHeight="1">
-      <c r="A18" s="74" t="s">
+      <c r="A18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="74" t="s">
+      <c r="C18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="74" t="s">
+      <c r="D18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="74" t="s">
+      <c r="E18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="74" t="s">
+      <c r="F18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="74" t="s">
+      <c r="G18" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="74" t="s">
+      <c r="H18" s="73" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="75" t="s">
+      <c r="G19" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="75" t="s">
+      <c r="H19" s="74" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="74" t="s">
+      <c r="E20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="74" t="s">
+      <c r="F20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="74" t="s">
+      <c r="G20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="74" t="s">
+      <c r="H20" s="73" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2291,89 +2295,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="82" t="s">
+      <c r="F1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="82" t="s">
+      <c r="G1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="H1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="82" t="s">
+      <c r="I1" s="81" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="83" t="s">
+      <c r="H2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="82" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="84" t="s">
+      <c r="H3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="84" t="s">
+      <c r="I3" s="83" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2553,43 +2557,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -2639,7 +2643,7 @@
       <c r="F5" s="44">
         <v>0</v>
       </c>
-      <c r="G5" s="67"/>
+      <c r="G5" s="66"/>
       <c r="H5" s="47"/>
       <c r="I5" s="48"/>
     </row>
@@ -2662,7 +2666,7 @@
       <c r="F6" s="45">
         <v>0</v>
       </c>
-      <c r="G6" s="68"/>
+      <c r="G6" s="67"/>
       <c r="H6" s="49"/>
       <c r="I6" s="50"/>
     </row>
@@ -2685,7 +2689,7 @@
       <c r="F7" s="46">
         <v>0</v>
       </c>
-      <c r="G7" s="69"/>
+      <c r="G7" s="68"/>
       <c r="H7" s="51"/>
       <c r="I7" s="52"/>
     </row>
@@ -2708,7 +2712,7 @@
       <c r="F8" s="45">
         <v>0</v>
       </c>
-      <c r="G8" s="68"/>
+      <c r="G8" s="67"/>
       <c r="H8" s="49"/>
       <c r="I8" s="50"/>
     </row>
@@ -2731,7 +2735,7 @@
       <c r="F9" s="46">
         <v>0</v>
       </c>
-      <c r="G9" s="69"/>
+      <c r="G9" s="68"/>
       <c r="H9" s="51"/>
       <c r="I9" s="52"/>
     </row>
@@ -2754,7 +2758,7 @@
       <c r="F10" s="45">
         <v>0</v>
       </c>
-      <c r="G10" s="68"/>
+      <c r="G10" s="67"/>
       <c r="H10" s="49"/>
       <c r="I10" s="50"/>
     </row>
@@ -2777,7 +2781,7 @@
       <c r="F11" s="46">
         <v>0</v>
       </c>
-      <c r="G11" s="69"/>
+      <c r="G11" s="68"/>
       <c r="H11" s="51"/>
       <c r="I11" s="52"/>
     </row>
@@ -2800,7 +2804,7 @@
       <c r="F12" s="45">
         <v>0</v>
       </c>
-      <c r="G12" s="68"/>
+      <c r="G12" s="67"/>
       <c r="H12" s="49"/>
       <c r="I12" s="50"/>
     </row>
@@ -2823,7 +2827,7 @@
       <c r="F13" s="46">
         <v>0</v>
       </c>
-      <c r="G13" s="69"/>
+      <c r="G13" s="68"/>
       <c r="H13" s="51"/>
       <c r="I13" s="52"/>
     </row>
@@ -2846,7 +2850,7 @@
       <c r="F14" s="45">
         <v>0</v>
       </c>
-      <c r="G14" s="68"/>
+      <c r="G14" s="67"/>
       <c r="H14" s="49"/>
       <c r="I14" s="50"/>
     </row>
@@ -2869,7 +2873,7 @@
       <c r="F15" s="46">
         <v>0</v>
       </c>
-      <c r="G15" s="69"/>
+      <c r="G15" s="68"/>
       <c r="H15" s="51"/>
       <c r="I15" s="52"/>
     </row>
@@ -2892,7 +2896,7 @@
       <c r="F16" s="46">
         <v>0</v>
       </c>
-      <c r="G16" s="69"/>
+      <c r="G16" s="68"/>
       <c r="H16" s="51"/>
       <c r="I16" s="52"/>
     </row>
@@ -2915,7 +2919,7 @@
       <c r="F17" s="45">
         <v>0</v>
       </c>
-      <c r="G17" s="68"/>
+      <c r="G17" s="67"/>
       <c r="H17" s="49"/>
       <c r="I17" s="50"/>
     </row>
@@ -2938,7 +2942,7 @@
       <c r="F18" s="46">
         <v>0</v>
       </c>
-      <c r="G18" s="69"/>
+      <c r="G18" s="68"/>
       <c r="H18" s="51"/>
       <c r="I18" s="52"/>
     </row>
@@ -2961,7 +2965,7 @@
       <c r="F19" s="45">
         <v>0</v>
       </c>
-      <c r="G19" s="68"/>
+      <c r="G19" s="67"/>
       <c r="H19" s="49"/>
       <c r="I19" s="50"/>
     </row>
@@ -2984,7 +2988,7 @@
       <c r="F20" s="46">
         <v>0</v>
       </c>
-      <c r="G20" s="69"/>
+      <c r="G20" s="68"/>
       <c r="H20" s="51"/>
       <c r="I20" s="52"/>
     </row>
@@ -3007,7 +3011,7 @@
       <c r="F21" s="45">
         <v>0</v>
       </c>
-      <c r="G21" s="68"/>
+      <c r="G21" s="67"/>
       <c r="H21" s="49"/>
       <c r="I21" s="50"/>
     </row>
@@ -3030,7 +3034,7 @@
       <c r="F22" s="46">
         <v>0</v>
       </c>
-      <c r="G22" s="69"/>
+      <c r="G22" s="68"/>
       <c r="H22" s="51"/>
       <c r="I22" s="52"/>
     </row>
@@ -3053,7 +3057,7 @@
       <c r="F23" s="45">
         <v>0</v>
       </c>
-      <c r="G23" s="68"/>
+      <c r="G23" s="67"/>
       <c r="H23" s="49"/>
       <c r="I23" s="50"/>
     </row>
@@ -3076,7 +3080,7 @@
       <c r="F24" s="46">
         <v>0</v>
       </c>
-      <c r="G24" s="69"/>
+      <c r="G24" s="68"/>
       <c r="H24" s="51"/>
       <c r="I24" s="52"/>
     </row>
@@ -3099,7 +3103,7 @@
       <c r="F25" s="45">
         <v>0</v>
       </c>
-      <c r="G25" s="68"/>
+      <c r="G25" s="67"/>
       <c r="H25" s="49"/>
       <c r="I25" s="50"/>
     </row>
@@ -3122,7 +3126,7 @@
       <c r="F26" s="46">
         <v>0</v>
       </c>
-      <c r="G26" s="69"/>
+      <c r="G26" s="68"/>
       <c r="H26" s="51"/>
       <c r="I26" s="52"/>
     </row>
@@ -3145,7 +3149,7 @@
       <c r="F27" s="45">
         <v>0</v>
       </c>
-      <c r="G27" s="68"/>
+      <c r="G27" s="67"/>
       <c r="H27" s="49"/>
       <c r="I27" s="50"/>
     </row>
@@ -3168,7 +3172,7 @@
       <c r="F28" s="46">
         <v>0</v>
       </c>
-      <c r="G28" s="69"/>
+      <c r="G28" s="68"/>
       <c r="H28" s="51"/>
       <c r="I28" s="52"/>
     </row>
@@ -3191,7 +3195,7 @@
       <c r="F29" s="45">
         <v>0</v>
       </c>
-      <c r="G29" s="68"/>
+      <c r="G29" s="67"/>
       <c r="H29" s="49"/>
       <c r="I29" s="50"/>
     </row>
@@ -3214,7 +3218,7 @@
       <c r="F30" s="46">
         <v>0</v>
       </c>
-      <c r="G30" s="69"/>
+      <c r="G30" s="68"/>
       <c r="H30" s="51"/>
       <c r="I30" s="52"/>
     </row>
@@ -3237,7 +3241,7 @@
       <c r="F31" s="45">
         <v>0</v>
       </c>
-      <c r="G31" s="68"/>
+      <c r="G31" s="67"/>
       <c r="H31" s="49"/>
       <c r="I31" s="50"/>
     </row>
@@ -3260,7 +3264,7 @@
       <c r="F32" s="46">
         <v>0</v>
       </c>
-      <c r="G32" s="69"/>
+      <c r="G32" s="68"/>
       <c r="H32" s="51"/>
       <c r="I32" s="52"/>
     </row>
@@ -3283,7 +3287,7 @@
       <c r="F33" s="45">
         <v>0</v>
       </c>
-      <c r="G33" s="68"/>
+      <c r="G33" s="67"/>
       <c r="H33" s="49"/>
       <c r="I33" s="50"/>
     </row>
@@ -3306,7 +3310,7 @@
       <c r="F34" s="46">
         <v>0</v>
       </c>
-      <c r="G34" s="69"/>
+      <c r="G34" s="68"/>
       <c r="H34" s="51"/>
       <c r="I34" s="52"/>
     </row>
@@ -3329,7 +3333,7 @@
       <c r="F35" s="45">
         <v>0</v>
       </c>
-      <c r="G35" s="68">
+      <c r="G35" s="67">
         <v>4</v>
       </c>
       <c r="H35" s="49">
@@ -3358,7 +3362,7 @@
       <c r="F36" s="46">
         <v>0</v>
       </c>
-      <c r="G36" s="69">
+      <c r="G36" s="68">
         <v>5</v>
       </c>
       <c r="H36" s="51">
@@ -3387,7 +3391,7 @@
       <c r="F37" s="45">
         <v>0</v>
       </c>
-      <c r="G37" s="68">
+      <c r="G37" s="67">
         <v>5</v>
       </c>
       <c r="H37" s="49">
@@ -3416,7 +3420,7 @@
       <c r="F38" s="46">
         <v>0</v>
       </c>
-      <c r="G38" s="69">
+      <c r="G38" s="68">
         <v>6</v>
       </c>
       <c r="H38" s="51">
@@ -3445,7 +3449,7 @@
       <c r="F39" s="45">
         <v>0</v>
       </c>
-      <c r="G39" s="68">
+      <c r="G39" s="67">
         <v>6</v>
       </c>
       <c r="H39" s="49">
@@ -3474,7 +3478,7 @@
       <c r="F40" s="46">
         <v>0</v>
       </c>
-      <c r="G40" s="69">
+      <c r="G40" s="68">
         <v>6</v>
       </c>
       <c r="H40" s="51">
@@ -3503,7 +3507,7 @@
       <c r="F41" s="45">
         <v>0</v>
       </c>
-      <c r="G41" s="68">
+      <c r="G41" s="67">
         <v>6</v>
       </c>
       <c r="H41" s="49">
@@ -3532,7 +3536,7 @@
       <c r="F42" s="46">
         <v>0</v>
       </c>
-      <c r="G42" s="69">
+      <c r="G42" s="68">
         <v>7</v>
       </c>
       <c r="H42" s="51">
@@ -3561,7 +3565,7 @@
       <c r="F43" s="45">
         <v>0</v>
       </c>
-      <c r="G43" s="68">
+      <c r="G43" s="67">
         <v>9</v>
       </c>
       <c r="H43" s="49">
@@ -3590,7 +3594,7 @@
       <c r="F44" s="46">
         <v>0</v>
       </c>
-      <c r="G44" s="69">
+      <c r="G44" s="68">
         <v>10</v>
       </c>
       <c r="H44" s="51">
@@ -3619,7 +3623,7 @@
       <c r="F45" s="45">
         <v>0</v>
       </c>
-      <c r="G45" s="68">
+      <c r="G45" s="67">
         <v>11</v>
       </c>
       <c r="H45" s="49">
@@ -3648,7 +3652,7 @@
       <c r="F46" s="46">
         <v>0</v>
       </c>
-      <c r="G46" s="69">
+      <c r="G46" s="68">
         <v>12</v>
       </c>
       <c r="H46" s="51">
@@ -3677,7 +3681,7 @@
       <c r="F47" s="45">
         <v>0</v>
       </c>
-      <c r="G47" s="68">
+      <c r="G47" s="67">
         <v>13</v>
       </c>
       <c r="H47" s="49">
@@ -3706,7 +3710,7 @@
       <c r="F48" s="46">
         <v>0</v>
       </c>
-      <c r="G48" s="69"/>
+      <c r="G48" s="68"/>
       <c r="H48" s="51"/>
       <c r="I48" s="52"/>
     </row>
@@ -3729,10 +3733,10 @@
       <c r="F49" s="14">
         <v>0</v>
       </c>
-      <c r="G49" s="70">
+      <c r="G49" s="69">
         <v>4</v>
       </c>
-      <c r="H49" s="66">
+      <c r="H49" s="65">
         <v>0.86875000000000002</v>
       </c>
     </row>
@@ -3755,10 +3759,10 @@
       <c r="F50" s="14">
         <v>0</v>
       </c>
-      <c r="G50" s="70">
+      <c r="G50" s="69">
         <v>5</v>
       </c>
-      <c r="H50" s="66">
+      <c r="H50" s="65">
         <v>0.88194444444444442</v>
       </c>
     </row>
@@ -3781,7 +3785,7 @@
       <c r="F51" s="14">
         <v>0</v>
       </c>
-      <c r="G51" s="70"/>
+      <c r="G51" s="69"/>
     </row>
     <row r="52" spans="1:8" ht="28" customHeight="1">
       <c r="A52" s="1" t="s">
@@ -3802,10 +3806,10 @@
       <c r="F52" s="14">
         <v>0</v>
       </c>
-      <c r="G52" s="70">
+      <c r="G52" s="69">
         <v>6</v>
       </c>
-      <c r="H52" s="66">
+      <c r="H52" s="65">
         <v>0.8930555555555556</v>
       </c>
     </row>
@@ -3828,10 +3832,10 @@
       <c r="F53" s="14">
         <v>0</v>
       </c>
-      <c r="G53" s="70">
+      <c r="G53" s="69">
         <v>11</v>
       </c>
-      <c r="H53" s="66">
+      <c r="H53" s="65">
         <v>0.96388888888888891</v>
       </c>
     </row>
@@ -3854,10 +3858,10 @@
       <c r="F54" s="14">
         <v>0</v>
       </c>
-      <c r="G54" s="70">
+      <c r="G54" s="69">
         <v>12</v>
       </c>
-      <c r="H54" s="66">
+      <c r="H54" s="65">
         <v>0.97847222222222219</v>
       </c>
     </row>
@@ -3880,10 +3884,10 @@
       <c r="F55" s="14">
         <v>0</v>
       </c>
-      <c r="G55" s="70">
+      <c r="G55" s="69">
         <v>5</v>
       </c>
-      <c r="H55" s="66">
+      <c r="H55" s="65">
         <v>0.87847222222222221</v>
       </c>
     </row>
@@ -3906,10 +3910,10 @@
       <c r="F56" s="14">
         <v>0</v>
       </c>
-      <c r="G56" s="70">
+      <c r="G56" s="69">
         <v>8</v>
       </c>
-      <c r="H56" s="66">
+      <c r="H56" s="65">
         <v>0.92986111111111114</v>
       </c>
     </row>
@@ -3938,7 +3942,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -3955,89 +3959,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="82" t="s">
+      <c r="F1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="82" t="s">
+      <c r="G1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="H1" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="82" t="s">
+      <c r="I1" s="81" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="19" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="83" t="s">
+      <c r="H2" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="82" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="84" t="s">
+      <c r="H3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="84" t="s">
+      <c r="I3" s="83" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4590,7 +4594,7 @@
       <c r="G24" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H24" s="65">
+      <c r="H24" s="61">
         <v>20</v>
       </c>
     </row>
@@ -4616,7 +4620,7 @@
       <c r="G25" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H25" s="65">
+      <c r="H25" s="61">
         <v>20</v>
       </c>
     </row>
@@ -4642,7 +4646,7 @@
       <c r="G26" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H26" s="65">
+      <c r="H26" s="61">
         <v>20</v>
       </c>
     </row>
@@ -4668,7 +4672,33 @@
       <c r="G27" s="62">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H27" s="65">
+      <c r="H27" s="61">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="19" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="28">
+        <v>46319</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="62">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H28" s="61">
         <v>20</v>
       </c>
     </row>
@@ -4685,7 +4715,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F27 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F28 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4702,7 +4732,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -4713,28 +4743,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -7338,6 +7368,146 @@
       </c>
       <c r="D189" s="14">
         <v>36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="25" customHeight="1">
+      <c r="A190" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C190" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="D190" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="25" customHeight="1">
+      <c r="A191" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C191" s="14">
+        <v>20</v>
+      </c>
+      <c r="D191" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="25" customHeight="1">
+      <c r="A192" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C192" s="14">
+        <v>20</v>
+      </c>
+      <c r="D192" s="14">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="25" customHeight="1">
+      <c r="A193" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C193" s="14">
+        <v>20</v>
+      </c>
+      <c r="D193" s="14">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="25" customHeight="1">
+      <c r="A194" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C194" s="14">
+        <v>20</v>
+      </c>
+      <c r="D194" s="14">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="25" customHeight="1">
+      <c r="A195" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C195" s="14">
+        <v>20</v>
+      </c>
+      <c r="D195" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="25" customHeight="1">
+      <c r="A196" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C196" s="14">
+        <v>40</v>
+      </c>
+      <c r="D196" s="14">
+        <v>82.6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="25" customHeight="1">
+      <c r="A197" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C197" s="14">
+        <v>55</v>
+      </c>
+      <c r="D197" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="25" customHeight="1">
+      <c r="A198" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C198" s="14">
+        <v>25</v>
+      </c>
+      <c r="D198" s="14">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="25" customHeight="1">
+      <c r="A199" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C199" s="14">
+        <v>20</v>
+      </c>
+      <c r="D199" s="14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7376,53 +7546,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="81" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="82" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="83" t="s">
         <v>118</v>
       </c>
     </row>
@@ -7549,71 +7719,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="82" t="s">
+      <c r="F1" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="82" t="s">
+      <c r="G1" s="81" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="82" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="83" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7727,31 +7897,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="89" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="63" t="s">

--- a/data/source/a-town-poker-data.xlsx
+++ b/data/source/a-town-poker-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthewoliver/Documents/Coding/ATownPokerSite/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F9B0FD-D043-2542-90CA-3B9D92EFE9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921DCF57-E1B9-274F-90FE-2466286AAF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="183">
   <si>
     <t>A-TOWN POKER</t>
   </si>
@@ -583,6 +583,12 @@
   </si>
   <si>
     <t>Saturday 10/24/26</t>
+  </si>
+  <si>
+    <t>cash-game-2026-10-28</t>
+  </si>
+  <si>
+    <t>Wednesday 10/28/26</t>
   </si>
 </sst>
 </file>
@@ -1519,7 +1525,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I28" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CashGamesTable" displayName="CashGamesTable" ref="A4:I29" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cash Game ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Slug"/>
@@ -1536,7 +1542,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D199" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CashGameResultsTable" displayName="CashGameResultsTable" ref="A4:D206" totalsRowShown="0" dataDxfId="28">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D21">
     <sortCondition ref="A15:A21"/>
   </sortState>
@@ -1979,7 +1985,7 @@
       </c>
       <c r="H8" s="40">
         <f>COUNTA('Cash Games'!A5:A500)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
@@ -2060,7 +2066,7 @@
       </c>
       <c r="H11" s="41">
         <f>COUNTA('Tournament Results'!A5:A509)+COUNTA('Cash Game Results'!A5:A499)</f>
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1"/>
@@ -3942,7 +3948,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -4702,6 +4708,32 @@
         <v>20</v>
       </c>
     </row>
+    <row r="29" spans="1:8" ht="19" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="28">
+        <v>46323</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="62">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H29" s="61">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4715,7 +4747,7 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="upcoming"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F28 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="F5:F29 G5:G199" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"completed,upcoming"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="I5:I199" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -4732,7 +4764,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="1" customWidth="1"/>
@@ -7508,6 +7540,104 @@
       </c>
       <c r="D199" s="14">
         <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="25" customHeight="1">
+      <c r="A200" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C200" s="14">
+        <v>20</v>
+      </c>
+      <c r="D200" s="14">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="25" customHeight="1">
+      <c r="A201" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C201" s="14">
+        <v>20</v>
+      </c>
+      <c r="D201" s="14">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="25" customHeight="1">
+      <c r="A202" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C202" s="14">
+        <v>40</v>
+      </c>
+      <c r="D202" s="14">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="25" customHeight="1">
+      <c r="A203" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C203" s="14">
+        <v>20</v>
+      </c>
+      <c r="D203" s="14">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="25" customHeight="1">
+      <c r="A204" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C204" s="14">
+        <v>20</v>
+      </c>
+      <c r="D204" s="14">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="25" customHeight="1">
+      <c r="A205" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C205" s="14">
+        <v>20</v>
+      </c>
+      <c r="D205" s="14">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="25" customHeight="1">
+      <c r="A206" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C206" s="14">
+        <v>40</v>
+      </c>
+      <c r="D206" s="14">
+        <v>14.25</v>
       </c>
     </row>
   </sheetData>
